--- a/.github/tmp_results.xlsx
+++ b/.github/tmp_results.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sean Elvidge\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sean Elvidge\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09D6CB8E-3577-40F1-B5E0-E8C203EA8820}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA7109CF-61DB-4E56-9C8D-8DCF5E39CCD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{156B8CF3-2535-45A6-80D2-358CC30668D6}"/>
+    <workbookView xWindow="28710" yWindow="2370" windowWidth="17580" windowHeight="13665" xr2:uid="{156B8CF3-2535-45A6-80D2-358CC30668D6}"/>
   </bookViews>
   <sheets>
     <sheet name="Scores" sheetId="1" r:id="rId1"/>
@@ -495,9 +495,6 @@
     <t>Away Team</t>
   </si>
   <si>
-    <t>Result</t>
-  </si>
-  <si>
     <t>4-0</t>
   </si>
   <si>
@@ -550,6 +547,9 @@
   </si>
   <si>
     <t>0-3</t>
+  </si>
+  <si>
+    <t>Score</t>
   </si>
 </sst>
 </file>
@@ -949,10 +949,10 @@
         <v>147</v>
       </c>
       <c r="E1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>152</v>
+        <v>170</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.35">
@@ -974,7 +974,7 @@
         <v>1</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.35">
@@ -996,7 +996,7 @@
         <v>2</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
@@ -1018,7 +1018,7 @@
         <v>4</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
@@ -1040,7 +1040,7 @@
         <v>1</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
@@ -1062,7 +1062,7 @@
         <v>1</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
@@ -1084,7 +1084,7 @@
         <v>1</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.35">
@@ -1106,7 +1106,7 @@
         <v>1</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.35">
@@ -1128,7 +1128,7 @@
         <v>2</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.35">
@@ -1150,7 +1150,7 @@
         <v>2</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.35">
@@ -1172,7 +1172,7 @@
         <v>2</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.35">
@@ -1194,7 +1194,7 @@
         <v>2</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.35">
@@ -1216,7 +1216,7 @@
         <v>2</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.35">
@@ -1238,7 +1238,7 @@
         <v>2</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.35">
@@ -1260,7 +1260,7 @@
         <v>2</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.35">
@@ -1282,7 +1282,7 @@
         <v>2</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.35">
@@ -1304,7 +1304,7 @@
         <v>2</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.35">
@@ -1326,7 +1326,7 @@
         <v>2</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.35">
@@ -1348,7 +1348,7 @@
         <v>3</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.35">
@@ -1370,7 +1370,7 @@
         <v>3</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.35">
@@ -1392,7 +1392,7 @@
         <v>3</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.35">
@@ -1414,7 +1414,7 @@
         <v>3</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.35">
@@ -1436,7 +1436,7 @@
         <v>3</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.35">
@@ -1458,7 +1458,7 @@
         <v>3</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.35">
@@ -1480,7 +1480,7 @@
         <v>3</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.35">
@@ -1502,7 +1502,7 @@
         <v>3</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.35">
@@ -1524,7 +1524,7 @@
         <v>3</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.35">
@@ -1546,7 +1546,7 @@
         <v>3</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.35">
@@ -1568,7 +1568,7 @@
         <v>4</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.35">
@@ -1590,7 +1590,7 @@
         <v>4</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.35">
@@ -1612,7 +1612,7 @@
         <v>4</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.35">
@@ -1634,7 +1634,7 @@
         <v>4</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.35">
@@ -1656,7 +1656,7 @@
         <v>4</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.35">
@@ -1678,7 +1678,7 @@
         <v>4</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.35">
@@ -1700,7 +1700,7 @@
         <v>4</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.35">
@@ -1722,7 +1722,7 @@
         <v>4</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.35">
@@ -1744,7 +1744,7 @@
         <v>4</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.35">
@@ -1766,7 +1766,7 @@
         <v>4</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.35">
@@ -1788,7 +1788,7 @@
         <v>4</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.35">
@@ -1810,7 +1810,7 @@
         <v>1</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.35">
@@ -1832,7 +1832,7 @@
         <v>1</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.35">
@@ -1854,7 +1854,7 @@
         <v>1</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.35">
@@ -1876,7 +1876,7 @@
         <v>1</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.35">
@@ -1898,7 +1898,7 @@
         <v>2</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
   </sheetData>

--- a/.github/tmp_results.xlsx
+++ b/.github/tmp_results.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sean Elvidge\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sean Elvidge\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA7109CF-61DB-4E56-9C8D-8DCF5E39CCD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85EE01EA-633B-43EE-86AC-0647EFE2668E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28710" yWindow="2370" windowWidth="17580" windowHeight="13665" xr2:uid="{156B8CF3-2535-45A6-80D2-358CC30668D6}"/>
+    <workbookView xWindow="20" yWindow="260" windowWidth="19180" windowHeight="11260" xr2:uid="{156B8CF3-2535-45A6-80D2-358CC30668D6}"/>
   </bookViews>
   <sheets>
     <sheet name="Scores" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="337" uniqueCount="171">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="155">
   <si>
     <t>AFC Bournemouth</t>
   </si>
@@ -495,61 +495,13 @@
     <t>Away Team</t>
   </si>
   <si>
-    <t>4-0</t>
-  </si>
-  <si>
-    <t>0-0</t>
-  </si>
-  <si>
-    <t>3-0</t>
+    <t>Result</t>
   </si>
   <si>
     <t>1-2</t>
   </si>
   <si>
-    <t>2-2</t>
-  </si>
-  <si>
-    <t>0-2</t>
-  </si>
-  <si>
-    <t>2-0</t>
-  </si>
-  <si>
-    <t>0-1</t>
-  </si>
-  <si>
-    <t>2-1</t>
-  </si>
-  <si>
     <t>Tier Ch</t>
-  </si>
-  <si>
-    <t>1-1</t>
-  </si>
-  <si>
-    <t>3-1</t>
-  </si>
-  <si>
-    <t>1-0</t>
-  </si>
-  <si>
-    <t>3-3</t>
-  </si>
-  <si>
-    <t>1-3</t>
-  </si>
-  <si>
-    <t>3-2</t>
-  </si>
-  <si>
-    <t>0-4</t>
-  </si>
-  <si>
-    <t>0-3</t>
-  </si>
-  <si>
-    <t>Score</t>
   </si>
 </sst>
 </file>
@@ -927,15 +879,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{944D37C4-CAD2-4526-8947-361FF9BC37B9}">
   <dimension ref="A1:F44"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.08984375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.90625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.85546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="23" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.7265625" style="3"/>
+    <col min="6" max="6" width="8.7109375" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>149</v>
       </c>
@@ -949,21 +901,21 @@
         <v>147</v>
       </c>
       <c r="E1" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B2" t="s">
-        <v>137</v>
+        <v>80</v>
       </c>
       <c r="C2" t="s">
-        <v>141</v>
+        <v>70</v>
       </c>
       <c r="D2">
         <f>VLOOKUP(B2,Teams!A:B,2,FALSE)</f>
@@ -974,932 +926,134 @@
         <v>1</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A3" s="2">
-        <v>46122</v>
-      </c>
-      <c r="B3" t="s">
-        <v>136</v>
-      </c>
-      <c r="C3" t="s">
-        <v>85</v>
-      </c>
-      <c r="D3">
-        <f>VLOOKUP(B3,Teams!A:B,2,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="E3">
-        <f>VLOOKUP(C3,Teams!A:B,2,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="F3" s="3" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A4" s="2">
-        <v>46122</v>
-      </c>
-      <c r="B4" t="s">
-        <v>40</v>
-      </c>
-      <c r="C4" t="s">
-        <v>129</v>
-      </c>
-      <c r="D4">
-        <f>VLOOKUP(B4,Teams!A:B,2,FALSE)</f>
-        <v>4</v>
-      </c>
-      <c r="E4">
-        <f>VLOOKUP(C4,Teams!A:B,2,FALSE)</f>
-        <v>4</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A5" s="2">
-        <v>46123</v>
-      </c>
-      <c r="B5" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5" t="s">
-        <v>0</v>
-      </c>
-      <c r="D5">
-        <f>VLOOKUP(B5,Teams!A:B,2,FALSE)</f>
-        <v>1</v>
-      </c>
-      <c r="E5">
-        <f>VLOOKUP(C5,Teams!A:B,2,FALSE)</f>
-        <v>1</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A6" s="2">
-        <v>46123</v>
-      </c>
-      <c r="B6" t="s">
-        <v>21</v>
-      </c>
-      <c r="C6" t="s">
-        <v>51</v>
-      </c>
-      <c r="D6">
-        <f>VLOOKUP(B6,Teams!A:B,2,FALSE)</f>
-        <v>1</v>
-      </c>
-      <c r="E6">
-        <f>VLOOKUP(C6,Teams!A:B,2,FALSE)</f>
-        <v>1</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A7" s="2">
-        <v>46123</v>
-      </c>
-      <c r="B7" t="s">
-        <v>26</v>
-      </c>
-      <c r="C7" t="s">
-        <v>22</v>
-      </c>
-      <c r="D7">
-        <f>VLOOKUP(B7,Teams!A:B,2,FALSE)</f>
-        <v>1</v>
-      </c>
-      <c r="E7">
-        <f>VLOOKUP(C7,Teams!A:B,2,FALSE)</f>
-        <v>1</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A8" s="2">
-        <v>46123</v>
-      </c>
-      <c r="B8" t="s">
-        <v>74</v>
-      </c>
-      <c r="C8" t="s">
-        <v>55</v>
-      </c>
-      <c r="D8">
-        <f>VLOOKUP(B8,Teams!A:B,2,FALSE)</f>
-        <v>1</v>
-      </c>
-      <c r="E8">
-        <f>VLOOKUP(C8,Teams!A:B,2,FALSE)</f>
-        <v>1</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A9" s="2">
-        <v>46123</v>
-      </c>
-      <c r="B9" t="s">
-        <v>41</v>
-      </c>
-      <c r="C9" t="s">
-        <v>116</v>
-      </c>
-      <c r="D9">
-        <f>VLOOKUP(B9,Teams!A:B,2,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="E9">
-        <f>VLOOKUP(C9,Teams!A:B,2,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A10" s="2">
-        <v>46123</v>
-      </c>
-      <c r="B10" t="s">
-        <v>95</v>
-      </c>
-      <c r="C10" t="s">
-        <v>67</v>
-      </c>
-      <c r="D10">
-        <f>VLOOKUP(B10,Teams!A:B,2,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="E10">
-        <f>VLOOKUP(C10,Teams!A:B,2,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A11" s="2">
-        <v>46123</v>
-      </c>
-      <c r="B11" t="s">
-        <v>105</v>
-      </c>
-      <c r="C11" t="s">
-        <v>23</v>
-      </c>
-      <c r="D11">
-        <f>VLOOKUP(B11,Teams!A:B,2,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="E11">
-        <f>VLOOKUP(C11,Teams!A:B,2,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A12" s="2">
-        <v>46123</v>
-      </c>
-      <c r="B12" t="s">
-        <v>35</v>
-      </c>
-      <c r="C12" t="s">
-        <v>104</v>
-      </c>
-      <c r="D12">
-        <f>VLOOKUP(B12,Teams!A:B,2,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="E12">
-        <f>VLOOKUP(C12,Teams!A:B,2,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A13" s="2">
-        <v>46123</v>
-      </c>
-      <c r="B13" t="s">
-        <v>71</v>
-      </c>
-      <c r="C13" t="s">
-        <v>128</v>
-      </c>
-      <c r="D13">
-        <f>VLOOKUP(B13,Teams!A:B,2,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="E13">
-        <f>VLOOKUP(C13,Teams!A:B,2,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A14" s="2">
-        <v>46123</v>
-      </c>
-      <c r="B14" t="s">
-        <v>83</v>
-      </c>
-      <c r="C14" t="s">
-        <v>103</v>
-      </c>
-      <c r="D14">
-        <f>VLOOKUP(B14,Teams!A:B,2,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="E14">
-        <f>VLOOKUP(C14,Teams!A:B,2,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A15" s="2">
-        <v>46123</v>
-      </c>
-      <c r="B15" t="s">
-        <v>99</v>
-      </c>
-      <c r="C15" t="s">
-        <v>135</v>
-      </c>
-      <c r="D15">
-        <f>VLOOKUP(B15,Teams!A:B,2,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="E15">
-        <f>VLOOKUP(C15,Teams!A:B,2,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A16" s="2">
-        <v>46123</v>
-      </c>
-      <c r="B16" t="s">
-        <v>115</v>
-      </c>
-      <c r="C16" t="s">
-        <v>66</v>
-      </c>
-      <c r="D16">
-        <f>VLOOKUP(B16,Teams!A:B,2,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="E16">
-        <f>VLOOKUP(C16,Teams!A:B,2,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="F16" s="3" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A17" s="2">
-        <v>46123</v>
-      </c>
-      <c r="B17" t="s">
-        <v>119</v>
-      </c>
-      <c r="C17" t="s">
-        <v>48</v>
-      </c>
-      <c r="D17">
-        <f>VLOOKUP(B17,Teams!A:B,2,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="E17">
-        <f>VLOOKUP(C17,Teams!A:B,2,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A18" s="2">
-        <v>46123</v>
-      </c>
-      <c r="B18" t="s">
-        <v>125</v>
-      </c>
-      <c r="C18" t="s">
-        <v>14</v>
-      </c>
-      <c r="D18">
-        <f>VLOOKUP(B18,Teams!A:B,2,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="E18">
-        <f>VLOOKUP(C18,Teams!A:B,2,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="F18" s="3" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A19" s="2">
-        <v>46123</v>
-      </c>
-      <c r="B19" t="s">
-        <v>33</v>
-      </c>
-      <c r="C19" t="s">
-        <v>16</v>
-      </c>
-      <c r="D19">
-        <f>VLOOKUP(B19,Teams!A:B,2,FALSE)</f>
-        <v>3</v>
-      </c>
-      <c r="E19">
-        <f>VLOOKUP(C19,Teams!A:B,2,FALSE)</f>
-        <v>3</v>
-      </c>
-      <c r="F19" s="3" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A20" s="2">
-        <v>46123</v>
-      </c>
-      <c r="B20" t="s">
-        <v>73</v>
-      </c>
-      <c r="C20" t="s">
-        <v>72</v>
-      </c>
-      <c r="D20">
-        <f>VLOOKUP(B20,Teams!A:B,2,FALSE)</f>
-        <v>3</v>
-      </c>
-      <c r="E20">
-        <f>VLOOKUP(C20,Teams!A:B,2,FALSE)</f>
-        <v>3</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A21" s="2">
-        <v>46123</v>
-      </c>
-      <c r="B21" t="s">
-        <v>101</v>
-      </c>
-      <c r="C21" t="s">
-        <v>52</v>
-      </c>
-      <c r="D21">
-        <f>VLOOKUP(B21,Teams!A:B,2,FALSE)</f>
-        <v>3</v>
-      </c>
-      <c r="E21">
-        <f>VLOOKUP(C21,Teams!A:B,2,FALSE)</f>
-        <v>3</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A22" s="2">
-        <v>46123</v>
-      </c>
-      <c r="B22" t="s">
-        <v>15</v>
-      </c>
-      <c r="C22" t="s">
-        <v>100</v>
-      </c>
-      <c r="D22">
-        <f>VLOOKUP(B22,Teams!A:B,2,FALSE)</f>
-        <v>3</v>
-      </c>
-      <c r="E22">
-        <f>VLOOKUP(C22,Teams!A:B,2,FALSE)</f>
-        <v>3</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A23" s="2">
-        <v>46123</v>
-      </c>
-      <c r="B23" t="s">
-        <v>19</v>
-      </c>
-      <c r="C23" t="s">
-        <v>123</v>
-      </c>
-      <c r="D23">
-        <f>VLOOKUP(B23,Teams!A:B,2,FALSE)</f>
-        <v>3</v>
-      </c>
-      <c r="E23">
-        <f>VLOOKUP(C23,Teams!A:B,2,FALSE)</f>
-        <v>3</v>
-      </c>
-      <c r="F23" s="3" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A24" s="2">
-        <v>46123</v>
-      </c>
-      <c r="B24" t="s">
-        <v>27</v>
-      </c>
-      <c r="C24" t="s">
-        <v>1</v>
-      </c>
-      <c r="D24">
-        <f>VLOOKUP(B24,Teams!A:B,2,FALSE)</f>
-        <v>3</v>
-      </c>
-      <c r="E24">
-        <f>VLOOKUP(C24,Teams!A:B,2,FALSE)</f>
-        <v>3</v>
-      </c>
-      <c r="F24" s="3" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A25" s="2">
-        <v>46123</v>
-      </c>
-      <c r="B25" t="s">
-        <v>49</v>
-      </c>
-      <c r="C25" t="s">
-        <v>106</v>
-      </c>
-      <c r="D25">
-        <f>VLOOKUP(B25,Teams!A:B,2,FALSE)</f>
-        <v>3</v>
-      </c>
-      <c r="E25">
-        <f>VLOOKUP(C25,Teams!A:B,2,FALSE)</f>
-        <v>3</v>
-      </c>
-      <c r="F25" s="3" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A26" s="2">
-        <v>46123</v>
-      </c>
-      <c r="B26" t="s">
-        <v>65</v>
-      </c>
-      <c r="C26" t="s">
-        <v>144</v>
-      </c>
-      <c r="D26">
-        <f>VLOOKUP(B26,Teams!A:B,2,FALSE)</f>
-        <v>3</v>
-      </c>
-      <c r="E26">
-        <f>VLOOKUP(C26,Teams!A:B,2,FALSE)</f>
-        <v>3</v>
-      </c>
-      <c r="F26" s="3" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A27" s="2">
-        <v>46123</v>
-      </c>
-      <c r="B27" t="s">
-        <v>110</v>
-      </c>
-      <c r="C27" t="s">
-        <v>11</v>
-      </c>
-      <c r="D27">
-        <f>VLOOKUP(B27,Teams!A:B,2,FALSE)</f>
-        <v>3</v>
-      </c>
-      <c r="E27">
-        <f>VLOOKUP(C27,Teams!A:B,2,FALSE)</f>
-        <v>3</v>
-      </c>
-      <c r="F27" s="3" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A28" s="2">
-        <v>46123</v>
-      </c>
-      <c r="B28" t="s">
-        <v>138</v>
-      </c>
-      <c r="C28" t="s">
-        <v>81</v>
-      </c>
-      <c r="D28">
-        <f>VLOOKUP(B28,Teams!A:B,2,FALSE)</f>
-        <v>3</v>
-      </c>
-      <c r="E28">
-        <f>VLOOKUP(C28,Teams!A:B,2,FALSE)</f>
-        <v>3</v>
-      </c>
-      <c r="F28" s="3" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A29" s="2">
-        <v>46123</v>
-      </c>
-      <c r="B29" t="s">
-        <v>24</v>
-      </c>
-      <c r="C29" t="s">
-        <v>42</v>
-      </c>
-      <c r="D29">
-        <f>VLOOKUP(B29,Teams!A:B,2,FALSE)</f>
-        <v>4</v>
-      </c>
-      <c r="E29">
-        <f>VLOOKUP(C29,Teams!A:B,2,FALSE)</f>
-        <v>4</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A30" s="2">
-        <v>46123</v>
-      </c>
-      <c r="B30" t="s">
-        <v>86</v>
-      </c>
-      <c r="C30" t="s">
-        <v>25</v>
-      </c>
-      <c r="D30">
-        <f>VLOOKUP(B30,Teams!A:B,2,FALSE)</f>
-        <v>4</v>
-      </c>
-      <c r="E30">
-        <f>VLOOKUP(C30,Teams!A:B,2,FALSE)</f>
-        <v>4</v>
-      </c>
-      <c r="F30" s="3" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A31" s="2">
-        <v>46123</v>
-      </c>
-      <c r="B31" t="s">
-        <v>4</v>
-      </c>
-      <c r="C31" t="s">
-        <v>53</v>
-      </c>
-      <c r="D31">
-        <f>VLOOKUP(B31,Teams!A:B,2,FALSE)</f>
-        <v>4</v>
-      </c>
-      <c r="E31">
-        <f>VLOOKUP(C31,Teams!A:B,2,FALSE)</f>
-        <v>4</v>
-      </c>
-      <c r="F31" s="3" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A32" s="2">
-        <v>46123</v>
-      </c>
-      <c r="B32" t="s">
-        <v>10</v>
-      </c>
-      <c r="C32" t="s">
-        <v>12</v>
-      </c>
-      <c r="D32">
-        <f>VLOOKUP(B32,Teams!A:B,2,FALSE)</f>
-        <v>4</v>
-      </c>
-      <c r="E32">
-        <f>VLOOKUP(C32,Teams!A:B,2,FALSE)</f>
-        <v>4</v>
-      </c>
-      <c r="F32" s="3" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A33" s="2">
-        <v>46123</v>
-      </c>
-      <c r="B33" t="s">
-        <v>32</v>
-      </c>
-      <c r="C33" t="s">
-        <v>97</v>
-      </c>
-      <c r="D33">
-        <f>VLOOKUP(B33,Teams!A:B,2,FALSE)</f>
-        <v>4</v>
-      </c>
-      <c r="E33">
-        <f>VLOOKUP(C33,Teams!A:B,2,FALSE)</f>
-        <v>4</v>
-      </c>
-      <c r="F33" s="3" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A34" s="2">
-        <v>46123</v>
-      </c>
-      <c r="B34" t="s">
-        <v>39</v>
-      </c>
-      <c r="C34" t="s">
-        <v>133</v>
-      </c>
-      <c r="D34">
-        <f>VLOOKUP(B34,Teams!A:B,2,FALSE)</f>
-        <v>4</v>
-      </c>
-      <c r="E34">
-        <f>VLOOKUP(C34,Teams!A:B,2,FALSE)</f>
-        <v>4</v>
-      </c>
-      <c r="F34" s="3" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A35" s="2">
-        <v>46123</v>
-      </c>
-      <c r="B35" t="s">
-        <v>60</v>
-      </c>
-      <c r="C35" t="s">
-        <v>43</v>
-      </c>
-      <c r="D35">
-        <f>VLOOKUP(B35,Teams!A:B,2,FALSE)</f>
-        <v>4</v>
-      </c>
-      <c r="E35">
-        <f>VLOOKUP(C35,Teams!A:B,2,FALSE)</f>
-        <v>4</v>
-      </c>
-      <c r="F35" s="3" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A36" s="2">
-        <v>46123</v>
-      </c>
-      <c r="B36" t="s">
-        <v>92</v>
-      </c>
-      <c r="C36" t="s">
-        <v>62</v>
-      </c>
-      <c r="D36">
-        <f>VLOOKUP(B36,Teams!A:B,2,FALSE)</f>
-        <v>4</v>
-      </c>
-      <c r="E36">
-        <f>VLOOKUP(C36,Teams!A:B,2,FALSE)</f>
-        <v>4</v>
-      </c>
-      <c r="F36" s="3" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A37" s="2">
-        <v>46123</v>
-      </c>
-      <c r="B37" t="s">
-        <v>112</v>
-      </c>
-      <c r="C37" t="s">
-        <v>58</v>
-      </c>
-      <c r="D37">
-        <f>VLOOKUP(B37,Teams!A:B,2,FALSE)</f>
-        <v>4</v>
-      </c>
-      <c r="E37">
-        <f>VLOOKUP(C37,Teams!A:B,2,FALSE)</f>
-        <v>4</v>
-      </c>
-      <c r="F37" s="3" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A38" s="2">
-        <v>46123</v>
-      </c>
-      <c r="B38" t="s">
-        <v>117</v>
-      </c>
-      <c r="C38" t="s">
-        <v>98</v>
-      </c>
-      <c r="D38">
-        <f>VLOOKUP(B38,Teams!A:B,2,FALSE)</f>
-        <v>4</v>
-      </c>
-      <c r="E38">
-        <f>VLOOKUP(C38,Teams!A:B,2,FALSE)</f>
-        <v>4</v>
-      </c>
-      <c r="F38" s="3" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A39" s="2">
-        <v>46123</v>
-      </c>
-      <c r="B39" t="s">
-        <v>134</v>
-      </c>
-      <c r="C39" t="s">
-        <v>37</v>
-      </c>
-      <c r="D39">
-        <f>VLOOKUP(B39,Teams!A:B,2,FALSE)</f>
-        <v>4</v>
-      </c>
-      <c r="E39">
-        <f>VLOOKUP(C39,Teams!A:B,2,FALSE)</f>
-        <v>4</v>
-      </c>
-      <c r="F39" s="3" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A40" s="2">
-        <v>46124</v>
-      </c>
-      <c r="B40" t="s">
-        <v>44</v>
-      </c>
-      <c r="C40" t="s">
-        <v>91</v>
-      </c>
-      <c r="D40">
-        <f>VLOOKUP(B40,Teams!A:B,2,FALSE)</f>
-        <v>1</v>
-      </c>
-      <c r="E40">
-        <f>VLOOKUP(C40,Teams!A:B,2,FALSE)</f>
-        <v>1</v>
-      </c>
-      <c r="F40" s="3" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A41" s="2">
-        <v>46124</v>
-      </c>
-      <c r="B41" t="s">
-        <v>96</v>
-      </c>
-      <c r="C41" t="s">
-        <v>9</v>
-      </c>
-      <c r="D41">
-        <f>VLOOKUP(B41,Teams!A:B,2,FALSE)</f>
-        <v>1</v>
-      </c>
-      <c r="E41">
-        <f>VLOOKUP(C41,Teams!A:B,2,FALSE)</f>
-        <v>1</v>
-      </c>
-      <c r="F41" s="3" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A42" s="2">
-        <v>46124</v>
-      </c>
-      <c r="B42" t="s">
-        <v>126</v>
-      </c>
-      <c r="C42" t="s">
-        <v>132</v>
-      </c>
-      <c r="D42">
-        <f>VLOOKUP(B42,Teams!A:B,2,FALSE)</f>
-        <v>1</v>
-      </c>
-      <c r="E42">
-        <f>VLOOKUP(C42,Teams!A:B,2,FALSE)</f>
-        <v>1</v>
-      </c>
-      <c r="F42" s="3" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A43" s="2">
-        <v>46124</v>
-      </c>
-      <c r="B43" t="s">
-        <v>36</v>
-      </c>
-      <c r="C43" t="s">
-        <v>79</v>
-      </c>
-      <c r="D43">
-        <f>VLOOKUP(B43,Teams!A:B,2,FALSE)</f>
-        <v>1</v>
-      </c>
-      <c r="E43">
-        <f>VLOOKUP(C43,Teams!A:B,2,FALSE)</f>
-        <v>1</v>
-      </c>
-      <c r="F43" s="3" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A44" s="2">
-        <v>46124</v>
-      </c>
-      <c r="B44" t="s">
-        <v>13</v>
-      </c>
-      <c r="C44" t="s">
-        <v>143</v>
-      </c>
-      <c r="D44">
-        <f>VLOOKUP(B44,Teams!A:B,2,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="E44">
-        <f>VLOOKUP(C44,Teams!A:B,2,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="F44" s="3" t="s">
-        <v>158</v>
-      </c>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="2"/>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="2"/>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="2"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="2"/>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="2"/>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="2"/>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="2"/>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="2"/>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="2"/>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="2"/>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="2"/>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="2"/>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="2"/>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="2"/>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17" s="2"/>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A18" s="2"/>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A19" s="2"/>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A20" s="2"/>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A21" s="2"/>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A22" s="2"/>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A23" s="2"/>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A24" s="2"/>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A25" s="2"/>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A26" s="2"/>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A27" s="2"/>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A28" s="2"/>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A29" s="2"/>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A30" s="2"/>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A31" s="2"/>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A32" s="2"/>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A33" s="2"/>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A34" s="2"/>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A35" s="2"/>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A36" s="2"/>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A37" s="2"/>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A38" s="2"/>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A39" s="2"/>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A40" s="2"/>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A41" s="2"/>
+    </row>
+    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A42" s="2"/>
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A43" s="2"/>
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A44" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1921,13 +1075,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{660D5CBD-EF61-4F28-8F5F-C3B953B1D14A}">
   <dimension ref="A1:B147"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="23" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.7265625" style="1"/>
+    <col min="2" max="2" width="8.7109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1935,7 +1089,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -1943,7 +1097,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -1951,7 +1105,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1959,7 +1113,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -1967,7 +1121,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -1975,7 +1129,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -1983,7 +1137,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -1991,7 +1145,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>8</v>
       </c>
@@ -1999,7 +1153,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>9</v>
       </c>
@@ -2007,7 +1161,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>10</v>
       </c>
@@ -2015,7 +1169,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>11</v>
       </c>
@@ -2023,7 +1177,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>12</v>
       </c>
@@ -2031,7 +1185,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>13</v>
       </c>
@@ -2039,7 +1193,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>14</v>
       </c>
@@ -2047,7 +1201,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>15</v>
       </c>
@@ -2055,7 +1209,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>16</v>
       </c>
@@ -2063,7 +1217,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>17</v>
       </c>
@@ -2071,7 +1225,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>18</v>
       </c>
@@ -2079,7 +1233,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>19</v>
       </c>
@@ -2087,7 +1241,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>20</v>
       </c>
@@ -2095,7 +1249,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>21</v>
       </c>
@@ -2103,7 +1257,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>22</v>
       </c>
@@ -2111,7 +1265,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>23</v>
       </c>
@@ -2119,7 +1273,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>24</v>
       </c>
@@ -2127,7 +1281,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>25</v>
       </c>
@@ -2135,7 +1289,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>26</v>
       </c>
@@ -2143,7 +1297,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>27</v>
       </c>
@@ -2151,7 +1305,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>28</v>
       </c>
@@ -2159,7 +1313,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>29</v>
       </c>
@@ -2167,7 +1321,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>30</v>
       </c>
@@ -2175,7 +1329,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>31</v>
       </c>
@@ -2183,7 +1337,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>32</v>
       </c>
@@ -2191,7 +1345,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>33</v>
       </c>
@@ -2199,7 +1353,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>34</v>
       </c>
@@ -2207,7 +1361,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>35</v>
       </c>
@@ -2215,7 +1369,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>36</v>
       </c>
@@ -2223,7 +1377,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>37</v>
       </c>
@@ -2231,7 +1385,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>38</v>
       </c>
@@ -2239,7 +1393,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>39</v>
       </c>
@@ -2247,7 +1401,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>40</v>
       </c>
@@ -2255,7 +1409,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>41</v>
       </c>
@@ -2263,7 +1417,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>42</v>
       </c>
@@ -2271,7 +1425,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>43</v>
       </c>
@@ -2279,7 +1433,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>44</v>
       </c>
@@ -2287,7 +1441,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>45</v>
       </c>
@@ -2295,7 +1449,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>46</v>
       </c>
@@ -2303,7 +1457,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>47</v>
       </c>
@@ -2311,7 +1465,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>48</v>
       </c>
@@ -2319,7 +1473,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>49</v>
       </c>
@@ -2327,7 +1481,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>50</v>
       </c>
@@ -2335,7 +1489,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>51</v>
       </c>
@@ -2343,7 +1497,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>52</v>
       </c>
@@ -2351,7 +1505,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>53</v>
       </c>
@@ -2359,7 +1513,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>54</v>
       </c>
@@ -2367,7 +1521,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>55</v>
       </c>
@@ -2375,7 +1529,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>56</v>
       </c>
@@ -2383,7 +1537,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>57</v>
       </c>
@@ -2391,7 +1545,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>58</v>
       </c>
@@ -2399,7 +1553,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>59</v>
       </c>
@@ -2407,7 +1561,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>60</v>
       </c>
@@ -2415,7 +1569,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>61</v>
       </c>
@@ -2423,7 +1577,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>62</v>
       </c>
@@ -2431,7 +1585,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>63</v>
       </c>
@@ -2439,7 +1593,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>64</v>
       </c>
@@ -2447,7 +1601,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>65</v>
       </c>
@@ -2455,7 +1609,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>66</v>
       </c>
@@ -2463,7 +1617,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>67</v>
       </c>
@@ -2471,7 +1625,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>68</v>
       </c>
@@ -2479,7 +1633,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>69</v>
       </c>
@@ -2487,7 +1641,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>70</v>
       </c>
@@ -2495,7 +1649,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>71</v>
       </c>
@@ -2503,7 +1657,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>72</v>
       </c>
@@ -2511,7 +1665,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>73</v>
       </c>
@@ -2519,7 +1673,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>74</v>
       </c>
@@ -2527,7 +1681,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>75</v>
       </c>
@@ -2535,7 +1689,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>76</v>
       </c>
@@ -2543,7 +1697,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>77</v>
       </c>
@@ -2551,7 +1705,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>78</v>
       </c>
@@ -2559,7 +1713,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>79</v>
       </c>
@@ -2567,7 +1721,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>80</v>
       </c>
@@ -2575,7 +1729,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>81</v>
       </c>
@@ -2583,7 +1737,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>82</v>
       </c>
@@ -2591,7 +1745,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>83</v>
       </c>
@@ -2599,7 +1753,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>84</v>
       </c>
@@ -2607,7 +1761,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>85</v>
       </c>
@@ -2615,7 +1769,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>86</v>
       </c>
@@ -2623,7 +1777,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>87</v>
       </c>
@@ -2631,7 +1785,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>88</v>
       </c>
@@ -2639,7 +1793,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>89</v>
       </c>
@@ -2647,7 +1801,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>90</v>
       </c>
@@ -2655,7 +1809,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>91</v>
       </c>
@@ -2663,7 +1817,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>92</v>
       </c>
@@ -2671,7 +1825,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>93</v>
       </c>
@@ -2679,7 +1833,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>94</v>
       </c>
@@ -2687,7 +1841,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>95</v>
       </c>
@@ -2695,7 +1849,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>96</v>
       </c>
@@ -2703,7 +1857,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>97</v>
       </c>
@@ -2711,7 +1865,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>98</v>
       </c>
@@ -2719,7 +1873,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>99</v>
       </c>
@@ -2727,7 +1881,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>100</v>
       </c>
@@ -2735,7 +1889,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="102" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>101</v>
       </c>
@@ -2743,7 +1897,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="103" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>102</v>
       </c>
@@ -2751,7 +1905,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="104" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>103</v>
       </c>
@@ -2759,7 +1913,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="105" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>104</v>
       </c>
@@ -2767,7 +1921,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="106" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>105</v>
       </c>
@@ -2775,7 +1929,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="107" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>106</v>
       </c>
@@ -2783,7 +1937,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="108" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>107</v>
       </c>
@@ -2791,7 +1945,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="109" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>108</v>
       </c>
@@ -2799,7 +1953,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="110" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>109</v>
       </c>
@@ -2807,7 +1961,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="111" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>110</v>
       </c>
@@ -2815,7 +1969,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="112" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>111</v>
       </c>
@@ -2823,7 +1977,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="113" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>112</v>
       </c>
@@ -2831,7 +1985,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="114" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>113</v>
       </c>
@@ -2839,7 +1993,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="115" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>114</v>
       </c>
@@ -2847,7 +2001,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="116" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>115</v>
       </c>
@@ -2855,7 +2009,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="117" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>116</v>
       </c>
@@ -2863,7 +2017,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="118" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>117</v>
       </c>
@@ -2871,7 +2025,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="119" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>118</v>
       </c>
@@ -2879,7 +2033,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="120" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>119</v>
       </c>
@@ -2887,7 +2041,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="121" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>120</v>
       </c>
@@ -2895,7 +2049,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="122" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>121</v>
       </c>
@@ -2903,7 +2057,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="123" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>122</v>
       </c>
@@ -2911,7 +2065,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="124" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>123</v>
       </c>
@@ -2919,7 +2073,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="125" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>124</v>
       </c>
@@ -2927,7 +2081,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="126" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>125</v>
       </c>
@@ -2935,7 +2089,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="127" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>126</v>
       </c>
@@ -2943,7 +2097,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="128" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>127</v>
       </c>
@@ -2951,7 +2105,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="129" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>128</v>
       </c>
@@ -2959,7 +2113,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="130" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>129</v>
       </c>
@@ -2967,7 +2121,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="131" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>130</v>
       </c>
@@ -2975,7 +2129,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="132" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>131</v>
       </c>
@@ -2983,7 +2137,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="133" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>132</v>
       </c>
@@ -2991,7 +2145,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="134" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>133</v>
       </c>
@@ -2999,7 +2153,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="135" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>134</v>
       </c>
@@ -3007,7 +2161,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="136" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>135</v>
       </c>
@@ -3015,7 +2169,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="137" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>136</v>
       </c>
@@ -3023,7 +2177,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="138" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>137</v>
       </c>
@@ -3031,7 +2185,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="139" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>138</v>
       </c>
@@ -3039,7 +2193,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="140" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>139</v>
       </c>
@@ -3047,7 +2201,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="141" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>140</v>
       </c>
@@ -3055,7 +2209,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="142" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>141</v>
       </c>
@@ -3063,7 +2217,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="143" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>142</v>
       </c>
@@ -3071,7 +2225,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="144" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>143</v>
       </c>
@@ -3079,7 +2233,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="145" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>144</v>
       </c>
@@ -3087,7 +2241,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="146" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>145</v>
       </c>
@@ -3095,7 +2249,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="147" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>146</v>
       </c>

--- a/.github/tmp_results.xlsx
+++ b/.github/tmp_results.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sean Elvidge\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sean Elvidge\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85EE01EA-633B-43EE-86AC-0647EFE2668E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45B6A5A8-71E0-4A18-98FE-63623CF71B23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20" yWindow="260" windowWidth="19180" windowHeight="11260" xr2:uid="{156B8CF3-2535-45A6-80D2-358CC30668D6}"/>
+    <workbookView xWindow="20" yWindow="720" windowWidth="19180" windowHeight="11280" xr2:uid="{156B8CF3-2535-45A6-80D2-358CC30668D6}"/>
   </bookViews>
   <sheets>
     <sheet name="Scores" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="161">
   <si>
     <t>AFC Bournemouth</t>
   </si>
@@ -498,10 +498,28 @@
     <t>Result</t>
   </si>
   <si>
-    <t>1-2</t>
-  </si>
-  <si>
     <t>Tier Ch</t>
+  </si>
+  <si>
+    <t>2-0</t>
+  </si>
+  <si>
+    <t>3-0</t>
+  </si>
+  <si>
+    <t>5-1</t>
+  </si>
+  <si>
+    <t>1-1</t>
+  </si>
+  <si>
+    <t>0-0</t>
+  </si>
+  <si>
+    <t>3-2</t>
+  </si>
+  <si>
+    <t>2-1</t>
   </si>
 </sst>
 </file>
@@ -901,7 +919,7 @@
         <v>147</v>
       </c>
       <c r="E1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F1" s="3" t="s">
         <v>152</v>
@@ -909,55 +927,245 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B2" t="s">
-        <v>80</v>
+        <v>103</v>
       </c>
       <c r="C2" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D2">
         <f>VLOOKUP(B2,Teams!A:B,2,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E2">
         <f>VLOOKUP(C2,Teams!A:B,2,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="2"/>
+      <c r="A3" s="2">
+        <v>46126</v>
+      </c>
+      <c r="B3" t="s">
+        <v>119</v>
+      </c>
+      <c r="C3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3">
+        <f>VLOOKUP(B3,Teams!A:B,2,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="E3">
+        <f>VLOOKUP(C3,Teams!A:B,2,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>155</v>
+      </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="2"/>
+      <c r="A4" s="2">
+        <v>46126</v>
+      </c>
+      <c r="B4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" t="s">
+        <v>123</v>
+      </c>
+      <c r="D4">
+        <f>VLOOKUP(B4,Teams!A:B,2,FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="E4">
+        <f>VLOOKUP(C4,Teams!A:B,2,FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>156</v>
+      </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="2"/>
+      <c r="A5" s="2">
+        <v>46126</v>
+      </c>
+      <c r="B5" t="s">
+        <v>65</v>
+      </c>
+      <c r="C5" t="s">
+        <v>33</v>
+      </c>
+      <c r="D5">
+        <f>VLOOKUP(B5,Teams!A:B,2,FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="E5">
+        <f>VLOOKUP(C5,Teams!A:B,2,FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>157</v>
+      </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="2"/>
+      <c r="A6" s="2">
+        <v>46126</v>
+      </c>
+      <c r="B6" t="s">
+        <v>72</v>
+      </c>
+      <c r="C6" t="s">
+        <v>81</v>
+      </c>
+      <c r="D6">
+        <f>VLOOKUP(B6,Teams!A:B,2,FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="E6">
+        <f>VLOOKUP(C6,Teams!A:B,2,FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>158</v>
+      </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="2"/>
+      <c r="A7" s="2">
+        <v>46126</v>
+      </c>
+      <c r="B7" t="s">
+        <v>102</v>
+      </c>
+      <c r="C7" t="s">
+        <v>11</v>
+      </c>
+      <c r="D7">
+        <f>VLOOKUP(B7,Teams!A:B,2,FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="E7">
+        <f>VLOOKUP(C7,Teams!A:B,2,FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>158</v>
+      </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="2"/>
+      <c r="A8" s="2">
+        <v>46126</v>
+      </c>
+      <c r="B8" t="s">
+        <v>138</v>
+      </c>
+      <c r="C8" t="s">
+        <v>110</v>
+      </c>
+      <c r="D8">
+        <f>VLOOKUP(B8,Teams!A:B,2,FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="E8">
+        <f>VLOOKUP(C8,Teams!A:B,2,FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>155</v>
+      </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="2"/>
+      <c r="A9" s="2">
+        <v>46126</v>
+      </c>
+      <c r="B9" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9" t="s">
+        <v>98</v>
+      </c>
+      <c r="D9">
+        <f>VLOOKUP(B9,Teams!A:B,2,FALSE)</f>
+        <v>4</v>
+      </c>
+      <c r="E9">
+        <f>VLOOKUP(C9,Teams!A:B,2,FALSE)</f>
+        <v>4</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>159</v>
+      </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="2"/>
+      <c r="A10" s="2">
+        <v>46126</v>
+      </c>
+      <c r="B10" t="s">
+        <v>37</v>
+      </c>
+      <c r="C10" t="s">
+        <v>58</v>
+      </c>
+      <c r="D10">
+        <f>VLOOKUP(B10,Teams!A:B,2,FALSE)</f>
+        <v>4</v>
+      </c>
+      <c r="E10">
+        <f>VLOOKUP(C10,Teams!A:B,2,FALSE)</f>
+        <v>4</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>160</v>
+      </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="2"/>
+      <c r="A11" s="2">
+        <v>46126</v>
+      </c>
+      <c r="B11" t="s">
+        <v>39</v>
+      </c>
+      <c r="C11" t="s">
+        <v>60</v>
+      </c>
+      <c r="D11">
+        <f>VLOOKUP(B11,Teams!A:B,2,FALSE)</f>
+        <v>4</v>
+      </c>
+      <c r="E11">
+        <f>VLOOKUP(C11,Teams!A:B,2,FALSE)</f>
+        <v>4</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>160</v>
+      </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="2"/>
+      <c r="A12" s="2">
+        <v>46126</v>
+      </c>
+      <c r="B12" t="s">
+        <v>40</v>
+      </c>
+      <c r="C12" t="s">
+        <v>4</v>
+      </c>
+      <c r="D12">
+        <f>VLOOKUP(B12,Teams!A:B,2,FALSE)</f>
+        <v>4</v>
+      </c>
+      <c r="E12">
+        <f>VLOOKUP(C12,Teams!A:B,2,FALSE)</f>
+        <v>4</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>160</v>
+      </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="2"/>

--- a/.github/tmp_results.xlsx
+++ b/.github/tmp_results.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sean Elvidge\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45B6A5A8-71E0-4A18-98FE-63623CF71B23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{968A3325-0BEF-459B-AB2F-E5F15E6B0882}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20" yWindow="720" windowWidth="19180" windowHeight="11280" xr2:uid="{156B8CF3-2535-45A6-80D2-358CC30668D6}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{156B8CF3-2535-45A6-80D2-358CC30668D6}"/>
   </bookViews>
   <sheets>
     <sheet name="Scores" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="167">
   <si>
     <t>AFC Bournemouth</t>
   </si>
@@ -507,19 +507,37 @@
     <t>3-0</t>
   </si>
   <si>
-    <t>5-1</t>
-  </si>
-  <si>
     <t>1-1</t>
   </si>
   <si>
     <t>0-0</t>
   </si>
   <si>
-    <t>3-2</t>
-  </si>
-  <si>
-    <t>2-1</t>
+    <t>1-2</t>
+  </si>
+  <si>
+    <t>2-2</t>
+  </si>
+  <si>
+    <t>1-0</t>
+  </si>
+  <si>
+    <t>2-4</t>
+  </si>
+  <si>
+    <t>0-2</t>
+  </si>
+  <si>
+    <t>3-3</t>
+  </si>
+  <si>
+    <t>1-3</t>
+  </si>
+  <si>
+    <t>0-1</t>
+  </si>
+  <si>
+    <t>1-4</t>
   </si>
 </sst>
 </file>
@@ -897,15 +915,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{944D37C4-CAD2-4526-8947-361FF9BC37B9}">
   <dimension ref="A1:F44"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.81640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="23" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.7109375" style="3"/>
+    <col min="6" max="6" width="8.7265625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>149</v>
       </c>
@@ -925,15 +943,15 @@
         <v>152</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" s="2">
-        <v>46126</v>
+        <v>46129</v>
       </c>
       <c r="B2" t="s">
-        <v>103</v>
+        <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>67</v>
+        <v>41</v>
       </c>
       <c r="D2">
         <f>VLOOKUP(B2,Teams!A:B,2,FALSE)</f>
@@ -944,323 +962,817 @@
         <v>2</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" s="2">
-        <v>46126</v>
+        <v>46130</v>
       </c>
       <c r="B3" t="s">
-        <v>119</v>
+        <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>14</v>
+        <v>55</v>
       </c>
       <c r="D3">
         <f>VLOOKUP(B3,Teams!A:B,2,FALSE)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E3">
         <f>VLOOKUP(C3,Teams!A:B,2,FALSE)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" s="2">
-        <v>46126</v>
+        <v>46130</v>
       </c>
       <c r="B4" t="s">
-        <v>16</v>
+        <v>70</v>
       </c>
       <c r="C4" t="s">
-        <v>123</v>
+        <v>141</v>
       </c>
       <c r="D4">
         <f>VLOOKUP(B4,Teams!A:B,2,FALSE)</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E4">
         <f>VLOOKUP(C4,Teams!A:B,2,FALSE)</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" s="2">
-        <v>46126</v>
+        <v>46130</v>
       </c>
       <c r="B5" t="s">
-        <v>65</v>
+        <v>91</v>
       </c>
       <c r="C5" t="s">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="D5">
         <f>VLOOKUP(B5,Teams!A:B,2,FALSE)</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E5">
         <f>VLOOKUP(C5,Teams!A:B,2,FALSE)</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" s="2">
-        <v>46126</v>
+        <v>46130</v>
       </c>
       <c r="B6" t="s">
-        <v>72</v>
+        <v>132</v>
       </c>
       <c r="C6" t="s">
-        <v>81</v>
+        <v>22</v>
       </c>
       <c r="D6">
         <f>VLOOKUP(B6,Teams!A:B,2,FALSE)</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E6">
         <f>VLOOKUP(C6,Teams!A:B,2,FALSE)</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" s="2">
-        <v>46126</v>
+        <v>46130</v>
       </c>
       <c r="B7" t="s">
-        <v>102</v>
+        <v>36</v>
       </c>
       <c r="C7" t="s">
-        <v>11</v>
+        <v>80</v>
       </c>
       <c r="D7">
         <f>VLOOKUP(B7,Teams!A:B,2,FALSE)</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E7">
         <f>VLOOKUP(C7,Teams!A:B,2,FALSE)</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" s="2">
-        <v>46126</v>
+        <v>46130</v>
       </c>
       <c r="B8" t="s">
-        <v>138</v>
+        <v>48</v>
       </c>
       <c r="C8" t="s">
-        <v>110</v>
+        <v>99</v>
       </c>
       <c r="D8">
         <f>VLOOKUP(B8,Teams!A:B,2,FALSE)</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E8">
         <f>VLOOKUP(C8,Teams!A:B,2,FALSE)</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" s="2">
-        <v>46126</v>
+        <v>46130</v>
       </c>
       <c r="B9" t="s">
-        <v>12</v>
+        <v>85</v>
       </c>
       <c r="C9" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="D9">
         <f>VLOOKUP(B9,Teams!A:B,2,FALSE)</f>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E9">
         <f>VLOOKUP(C9,Teams!A:B,2,FALSE)</f>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10" s="2">
-        <v>46126</v>
+        <v>46130</v>
       </c>
       <c r="B10" t="s">
-        <v>37</v>
+        <v>103</v>
       </c>
       <c r="C10" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="D10">
         <f>VLOOKUP(B10,Teams!A:B,2,FALSE)</f>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E10">
         <f>VLOOKUP(C10,Teams!A:B,2,FALSE)</f>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F10" s="3" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11" s="2">
-        <v>46126</v>
+        <v>46130</v>
       </c>
       <c r="B11" t="s">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="C11" t="s">
-        <v>60</v>
+        <v>95</v>
       </c>
       <c r="D11">
         <f>VLOOKUP(B11,Teams!A:B,2,FALSE)</f>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E11">
         <f>VLOOKUP(C11,Teams!A:B,2,FALSE)</f>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12" s="2">
-        <v>46126</v>
+        <v>46130</v>
       </c>
       <c r="B12" t="s">
-        <v>40</v>
+        <v>66</v>
       </c>
       <c r="C12" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="D12">
         <f>VLOOKUP(B12,Teams!A:B,2,FALSE)</f>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E12">
         <f>VLOOKUP(C12,Teams!A:B,2,FALSE)</f>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F12" s="3" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A13" s="2">
+        <v>46130</v>
+      </c>
+      <c r="B13" t="s">
+        <v>104</v>
+      </c>
+      <c r="C13" t="s">
+        <v>136</v>
+      </c>
+      <c r="D13">
+        <f>VLOOKUP(B13,Teams!A:B,2,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="E13">
+        <f>VLOOKUP(C13,Teams!A:B,2,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A14" s="2">
+        <v>46130</v>
+      </c>
+      <c r="B14" t="s">
+        <v>116</v>
+      </c>
+      <c r="C14" t="s">
+        <v>35</v>
+      </c>
+      <c r="D14">
+        <f>VLOOKUP(B14,Teams!A:B,2,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="E14">
+        <f>VLOOKUP(C14,Teams!A:B,2,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A15" s="2">
+        <v>46130</v>
+      </c>
+      <c r="B15" t="s">
+        <v>128</v>
+      </c>
+      <c r="C15" t="s">
+        <v>119</v>
+      </c>
+      <c r="D15">
+        <f>VLOOKUP(B15,Teams!A:B,2,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="E15">
+        <f>VLOOKUP(C15,Teams!A:B,2,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A16" s="2">
+        <v>46130</v>
+      </c>
+      <c r="B16" t="s">
+        <v>135</v>
+      </c>
+      <c r="C16" t="s">
+        <v>115</v>
+      </c>
+      <c r="D16">
+        <f>VLOOKUP(B16,Teams!A:B,2,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="E16">
+        <f>VLOOKUP(C16,Teams!A:B,2,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A17" s="2">
+        <v>46130</v>
+      </c>
+      <c r="B17" t="s">
+        <v>143</v>
+      </c>
+      <c r="C17" t="s">
+        <v>125</v>
+      </c>
+      <c r="D17">
+        <f>VLOOKUP(B17,Teams!A:B,2,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="E17">
+        <f>VLOOKUP(C17,Teams!A:B,2,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A18" s="2">
+        <v>46130</v>
+      </c>
+      <c r="B18" t="s">
+        <v>11</v>
+      </c>
+      <c r="C18" t="s">
+        <v>19</v>
+      </c>
+      <c r="D18">
+        <f>VLOOKUP(B18,Teams!A:B,2,FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="E18">
+        <f>VLOOKUP(C18,Teams!A:B,2,FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A19" s="2">
+        <v>46130</v>
+      </c>
+      <c r="B19" t="s">
+        <v>16</v>
+      </c>
+      <c r="C19" t="s">
+        <v>65</v>
+      </c>
+      <c r="D19">
+        <f>VLOOKUP(B19,Teams!A:B,2,FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="E19">
+        <f>VLOOKUP(C19,Teams!A:B,2,FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A20" s="2">
+        <v>46130</v>
+      </c>
+      <c r="B20" t="s">
+        <v>1</v>
+      </c>
+      <c r="C20" t="s">
+        <v>101</v>
+      </c>
+      <c r="D20">
+        <f>VLOOKUP(B20,Teams!A:B,2,FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="E20">
+        <f>VLOOKUP(C20,Teams!A:B,2,FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A21" s="2">
+        <v>46130</v>
+      </c>
+      <c r="B21" t="s">
+        <v>52</v>
+      </c>
+      <c r="C21" t="s">
+        <v>124</v>
+      </c>
+      <c r="D21">
+        <f>VLOOKUP(B21,Teams!A:B,2,FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="E21">
+        <f>VLOOKUP(C21,Teams!A:B,2,FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A22" s="2">
+        <v>46130</v>
+      </c>
+      <c r="B22" t="s">
+        <v>72</v>
+      </c>
+      <c r="C22" t="s">
+        <v>110</v>
+      </c>
+      <c r="D22">
+        <f>VLOOKUP(B22,Teams!A:B,2,FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="E22">
+        <f>VLOOKUP(C22,Teams!A:B,2,FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A23" s="2">
+        <v>46130</v>
+      </c>
+      <c r="B23" t="s">
+        <v>81</v>
+      </c>
+      <c r="C23" t="s">
+        <v>76</v>
+      </c>
+      <c r="D23">
+        <f>VLOOKUP(B23,Teams!A:B,2,FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="E23">
+        <f>VLOOKUP(C23,Teams!A:B,2,FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A24" s="2">
+        <v>46130</v>
+      </c>
+      <c r="B24" t="s">
+        <v>93</v>
+      </c>
+      <c r="C24" t="s">
+        <v>49</v>
+      </c>
+      <c r="D24">
+        <f>VLOOKUP(B24,Teams!A:B,2,FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="E24">
+        <f>VLOOKUP(C24,Teams!A:B,2,FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A25" s="2">
+        <v>46130</v>
+      </c>
+      <c r="B25" t="s">
+        <v>106</v>
+      </c>
+      <c r="C25" t="s">
+        <v>33</v>
+      </c>
+      <c r="D25">
+        <f>VLOOKUP(B25,Teams!A:B,2,FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="E25">
+        <f>VLOOKUP(C25,Teams!A:B,2,FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A26" s="2">
+        <v>46130</v>
+      </c>
+      <c r="B26" t="s">
+        <v>123</v>
+      </c>
+      <c r="C26" t="s">
+        <v>73</v>
+      </c>
+      <c r="D26">
+        <f>VLOOKUP(B26,Teams!A:B,2,FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="E26">
+        <f>VLOOKUP(C26,Teams!A:B,2,FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A27" s="2">
+        <v>46130</v>
+      </c>
+      <c r="B27" t="s">
+        <v>144</v>
+      </c>
+      <c r="C27" t="s">
+        <v>15</v>
+      </c>
+      <c r="D27">
+        <f>VLOOKUP(B27,Teams!A:B,2,FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="E27">
+        <f>VLOOKUP(C27,Teams!A:B,2,FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A28" s="2">
+        <v>46130</v>
+      </c>
+      <c r="B28" t="s">
+        <v>12</v>
+      </c>
+      <c r="C28" t="s">
+        <v>134</v>
+      </c>
+      <c r="D28">
+        <f>VLOOKUP(B28,Teams!A:B,2,FALSE)</f>
+        <v>4</v>
+      </c>
+      <c r="E28">
+        <f>VLOOKUP(C28,Teams!A:B,2,FALSE)</f>
+        <v>4</v>
+      </c>
+      <c r="F28" s="3" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A29" s="2">
+        <v>46130</v>
+      </c>
+      <c r="B29" t="s">
+        <v>129</v>
+      </c>
+      <c r="C29" t="s">
+        <v>4</v>
+      </c>
+      <c r="D29">
+        <f>VLOOKUP(B29,Teams!A:B,2,FALSE)</f>
+        <v>4</v>
+      </c>
+      <c r="E29">
+        <f>VLOOKUP(C29,Teams!A:B,2,FALSE)</f>
+        <v>4</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A30" s="2">
+        <v>46130</v>
+      </c>
+      <c r="B30" t="s">
+        <v>37</v>
+      </c>
+      <c r="C30" t="s">
+        <v>92</v>
+      </c>
+      <c r="D30">
+        <f>VLOOKUP(B30,Teams!A:B,2,FALSE)</f>
+        <v>4</v>
+      </c>
+      <c r="E30">
+        <f>VLOOKUP(C30,Teams!A:B,2,FALSE)</f>
+        <v>4</v>
+      </c>
+      <c r="F30" s="3" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="2"/>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="2"/>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="2"/>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="2"/>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" s="2"/>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A18" s="2"/>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19" s="2"/>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A20" s="2"/>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A21" s="2"/>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A22" s="2"/>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A23" s="2"/>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A24" s="2"/>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A25" s="2"/>
-    </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A26" s="2"/>
-    </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A27" s="2"/>
-    </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A28" s="2"/>
-    </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A29" s="2"/>
-    </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A30" s="2"/>
-    </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A31" s="2"/>
-    </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A32" s="2"/>
-    </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A33" s="2"/>
-    </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A34" s="2"/>
-    </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A35" s="2"/>
-    </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A36" s="2"/>
-    </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A37" s="2"/>
-    </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A38" s="2"/>
-    </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A31" s="2">
+        <v>46130</v>
+      </c>
+      <c r="B31" t="s">
+        <v>42</v>
+      </c>
+      <c r="C31" t="s">
+        <v>117</v>
+      </c>
+      <c r="D31">
+        <f>VLOOKUP(B31,Teams!A:B,2,FALSE)</f>
+        <v>4</v>
+      </c>
+      <c r="E31">
+        <f>VLOOKUP(C31,Teams!A:B,2,FALSE)</f>
+        <v>4</v>
+      </c>
+      <c r="F31" s="3" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A32" s="2">
+        <v>46130</v>
+      </c>
+      <c r="B32" t="s">
+        <v>43</v>
+      </c>
+      <c r="C32" t="s">
+        <v>86</v>
+      </c>
+      <c r="D32">
+        <f>VLOOKUP(B32,Teams!A:B,2,FALSE)</f>
+        <v>4</v>
+      </c>
+      <c r="E32">
+        <f>VLOOKUP(C32,Teams!A:B,2,FALSE)</f>
+        <v>4</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A33" s="2">
+        <v>46130</v>
+      </c>
+      <c r="B33" t="s">
+        <v>53</v>
+      </c>
+      <c r="C33" t="s">
+        <v>39</v>
+      </c>
+      <c r="D33">
+        <f>VLOOKUP(B33,Teams!A:B,2,FALSE)</f>
+        <v>4</v>
+      </c>
+      <c r="E33">
+        <f>VLOOKUP(C33,Teams!A:B,2,FALSE)</f>
+        <v>4</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A34" s="2">
+        <v>46130</v>
+      </c>
+      <c r="B34" t="s">
+        <v>58</v>
+      </c>
+      <c r="C34" t="s">
+        <v>60</v>
+      </c>
+      <c r="D34">
+        <f>VLOOKUP(B34,Teams!A:B,2,FALSE)</f>
+        <v>4</v>
+      </c>
+      <c r="E34">
+        <f>VLOOKUP(C34,Teams!A:B,2,FALSE)</f>
+        <v>4</v>
+      </c>
+      <c r="F34" s="3" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A35" s="2">
+        <v>46130</v>
+      </c>
+      <c r="B35" t="s">
+        <v>62</v>
+      </c>
+      <c r="C35" t="s">
+        <v>40</v>
+      </c>
+      <c r="D35">
+        <f>VLOOKUP(B35,Teams!A:B,2,FALSE)</f>
+        <v>4</v>
+      </c>
+      <c r="E35">
+        <f>VLOOKUP(C35,Teams!A:B,2,FALSE)</f>
+        <v>4</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A36" s="2">
+        <v>46130</v>
+      </c>
+      <c r="B36" t="s">
+        <v>97</v>
+      </c>
+      <c r="C36" t="s">
+        <v>10</v>
+      </c>
+      <c r="D36">
+        <f>VLOOKUP(B36,Teams!A:B,2,FALSE)</f>
+        <v>4</v>
+      </c>
+      <c r="E36">
+        <f>VLOOKUP(C36,Teams!A:B,2,FALSE)</f>
+        <v>4</v>
+      </c>
+      <c r="F36" s="3" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A37" s="2">
+        <v>46130</v>
+      </c>
+      <c r="B37" t="s">
+        <v>98</v>
+      </c>
+      <c r="C37" t="s">
+        <v>112</v>
+      </c>
+      <c r="D37">
+        <f>VLOOKUP(B37,Teams!A:B,2,FALSE)</f>
+        <v>4</v>
+      </c>
+      <c r="E37">
+        <f>VLOOKUP(C37,Teams!A:B,2,FALSE)</f>
+        <v>4</v>
+      </c>
+      <c r="F37" s="3" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A38" s="2">
+        <v>46130</v>
+      </c>
+      <c r="B38" t="s">
+        <v>133</v>
+      </c>
+      <c r="C38" t="s">
+        <v>24</v>
+      </c>
+      <c r="D38">
+        <f>VLOOKUP(B38,Teams!A:B,2,FALSE)</f>
+        <v>4</v>
+      </c>
+      <c r="E38">
+        <f>VLOOKUP(C38,Teams!A:B,2,FALSE)</f>
+        <v>4</v>
+      </c>
+      <c r="F38" s="3" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A39" s="2"/>
     </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A40" s="2"/>
     </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A41" s="2"/>
     </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A42" s="2"/>
     </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A43" s="2"/>
     </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A44" s="2"/>
     </row>
   </sheetData>
@@ -1283,13 +1795,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{660D5CBD-EF61-4F28-8F5F-C3B953B1D14A}">
   <dimension ref="A1:B147"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="23" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.7109375" style="1"/>
+    <col min="2" max="2" width="8.7265625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1297,7 +1809,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -1305,7 +1817,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -1313,7 +1825,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1321,7 +1833,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -1329,7 +1841,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -1337,7 +1849,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -1345,7 +1857,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -1353,7 +1865,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>8</v>
       </c>
@@ -1361,7 +1873,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>9</v>
       </c>
@@ -1369,7 +1881,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>10</v>
       </c>
@@ -1377,7 +1889,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>11</v>
       </c>
@@ -1385,7 +1897,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>12</v>
       </c>
@@ -1393,7 +1905,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>13</v>
       </c>
@@ -1401,7 +1913,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>14</v>
       </c>
@@ -1409,7 +1921,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>15</v>
       </c>
@@ -1417,7 +1929,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>16</v>
       </c>
@@ -1425,7 +1937,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>17</v>
       </c>
@@ -1433,7 +1945,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>18</v>
       </c>
@@ -1441,7 +1953,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>19</v>
       </c>
@@ -1449,7 +1961,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>20</v>
       </c>
@@ -1457,7 +1969,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>21</v>
       </c>
@@ -1465,7 +1977,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>22</v>
       </c>
@@ -1473,7 +1985,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>23</v>
       </c>
@@ -1481,7 +1993,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>24</v>
       </c>
@@ -1489,7 +2001,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>25</v>
       </c>
@@ -1497,7 +2009,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>26</v>
       </c>
@@ -1505,7 +2017,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>27</v>
       </c>
@@ -1513,7 +2025,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>28</v>
       </c>
@@ -1521,7 +2033,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>29</v>
       </c>
@@ -1529,7 +2041,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>30</v>
       </c>
@@ -1537,7 +2049,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>31</v>
       </c>
@@ -1545,7 +2057,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>32</v>
       </c>
@@ -1553,7 +2065,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>33</v>
       </c>
@@ -1561,7 +2073,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>34</v>
       </c>
@@ -1569,7 +2081,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>35</v>
       </c>
@@ -1577,7 +2089,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>36</v>
       </c>
@@ -1585,7 +2097,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>37</v>
       </c>
@@ -1593,7 +2105,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>38</v>
       </c>
@@ -1601,7 +2113,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>39</v>
       </c>
@@ -1609,7 +2121,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>40</v>
       </c>
@@ -1617,7 +2129,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>41</v>
       </c>
@@ -1625,7 +2137,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>42</v>
       </c>
@@ -1633,7 +2145,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>43</v>
       </c>
@@ -1641,7 +2153,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>44</v>
       </c>
@@ -1649,7 +2161,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>45</v>
       </c>
@@ -1657,7 +2169,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>46</v>
       </c>
@@ -1665,7 +2177,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>47</v>
       </c>
@@ -1673,7 +2185,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>48</v>
       </c>
@@ -1681,7 +2193,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>49</v>
       </c>
@@ -1689,7 +2201,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>50</v>
       </c>
@@ -1697,7 +2209,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>51</v>
       </c>
@@ -1705,7 +2217,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>52</v>
       </c>
@@ -1713,7 +2225,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>53</v>
       </c>
@@ -1721,7 +2233,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>54</v>
       </c>
@@ -1729,7 +2241,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>55</v>
       </c>
@@ -1737,7 +2249,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>56</v>
       </c>
@@ -1745,7 +2257,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>57</v>
       </c>
@@ -1753,7 +2265,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>58</v>
       </c>
@@ -1761,7 +2273,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>59</v>
       </c>
@@ -1769,7 +2281,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>60</v>
       </c>
@@ -1777,7 +2289,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>61</v>
       </c>
@@ -1785,7 +2297,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>62</v>
       </c>
@@ -1793,7 +2305,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>63</v>
       </c>
@@ -1801,7 +2313,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>64</v>
       </c>
@@ -1809,7 +2321,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>65</v>
       </c>
@@ -1817,7 +2329,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>66</v>
       </c>
@@ -1825,7 +2337,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>67</v>
       </c>
@@ -1833,7 +2345,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>68</v>
       </c>
@@ -1841,7 +2353,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>69</v>
       </c>
@@ -1849,7 +2361,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>70</v>
       </c>
@@ -1857,7 +2369,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>71</v>
       </c>
@@ -1865,7 +2377,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>72</v>
       </c>
@@ -1873,7 +2385,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>73</v>
       </c>
@@ -1881,7 +2393,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>74</v>
       </c>
@@ -1889,7 +2401,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>75</v>
       </c>
@@ -1897,7 +2409,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>76</v>
       </c>
@@ -1905,7 +2417,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
         <v>77</v>
       </c>
@@ -1913,7 +2425,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
         <v>78</v>
       </c>
@@ -1921,7 +2433,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
         <v>79</v>
       </c>
@@ -1929,7 +2441,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>80</v>
       </c>
@@ -1937,7 +2449,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
         <v>81</v>
       </c>
@@ -1945,7 +2457,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
         <v>82</v>
       </c>
@@ -1953,7 +2465,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
         <v>83</v>
       </c>
@@ -1961,7 +2473,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
         <v>84</v>
       </c>
@@ -1969,7 +2481,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
         <v>85</v>
       </c>
@@ -1977,7 +2489,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
         <v>86</v>
       </c>
@@ -1985,7 +2497,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
         <v>87</v>
       </c>
@@ -1993,7 +2505,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
         <v>88</v>
       </c>
@@ -2001,7 +2513,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
         <v>89</v>
       </c>
@@ -2009,7 +2521,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
         <v>90</v>
       </c>
@@ -2017,7 +2529,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
         <v>91</v>
       </c>
@@ -2025,7 +2537,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
         <v>92</v>
       </c>
@@ -2033,7 +2545,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
         <v>93</v>
       </c>
@@ -2041,7 +2553,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
         <v>94</v>
       </c>
@@ -2049,7 +2561,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
         <v>95</v>
       </c>
@@ -2057,7 +2569,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
         <v>96</v>
       </c>
@@ -2065,7 +2577,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
         <v>97</v>
       </c>
@@ -2073,7 +2585,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
         <v>98</v>
       </c>
@@ -2081,7 +2593,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
         <v>99</v>
       </c>
@@ -2089,7 +2601,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
         <v>100</v>
       </c>
@@ -2097,7 +2609,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="102" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
         <v>101</v>
       </c>
@@ -2105,7 +2617,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="103" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
         <v>102</v>
       </c>
@@ -2113,7 +2625,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="104" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
         <v>103</v>
       </c>
@@ -2121,7 +2633,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="105" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
         <v>104</v>
       </c>
@@ -2129,7 +2641,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="106" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
         <v>105</v>
       </c>
@@ -2137,7 +2649,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="107" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
         <v>106</v>
       </c>
@@ -2145,7 +2657,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="108" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
         <v>107</v>
       </c>
@@ -2153,7 +2665,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="109" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
         <v>108</v>
       </c>
@@ -2161,7 +2673,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="110" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
         <v>109</v>
       </c>
@@ -2169,7 +2681,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="111" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
         <v>110</v>
       </c>
@@ -2177,7 +2689,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="112" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
         <v>111</v>
       </c>
@@ -2185,7 +2697,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="113" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
         <v>112</v>
       </c>
@@ -2193,7 +2705,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="114" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
         <v>113</v>
       </c>
@@ -2201,7 +2713,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="115" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
         <v>114</v>
       </c>
@@ -2209,7 +2721,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="116" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
         <v>115</v>
       </c>
@@ -2217,7 +2729,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="117" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
         <v>116</v>
       </c>
@@ -2225,7 +2737,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="118" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
         <v>117</v>
       </c>
@@ -2233,7 +2745,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="119" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
         <v>118</v>
       </c>
@@ -2241,7 +2753,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="120" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
         <v>119</v>
       </c>
@@ -2249,7 +2761,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="121" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
         <v>120</v>
       </c>
@@ -2257,7 +2769,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="122" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
         <v>121</v>
       </c>
@@ -2265,7 +2777,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="123" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
         <v>122</v>
       </c>
@@ -2273,7 +2785,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="124" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
         <v>123</v>
       </c>
@@ -2281,7 +2793,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="125" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
         <v>124</v>
       </c>
@@ -2289,7 +2801,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="126" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
         <v>125</v>
       </c>
@@ -2297,7 +2809,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="127" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
         <v>126</v>
       </c>
@@ -2305,7 +2817,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="128" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
         <v>127</v>
       </c>
@@ -2313,7 +2825,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="129" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
         <v>128</v>
       </c>
@@ -2321,7 +2833,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="130" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
         <v>129</v>
       </c>
@@ -2329,7 +2841,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="131" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
         <v>130</v>
       </c>
@@ -2337,7 +2849,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="132" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
         <v>131</v>
       </c>
@@ -2345,7 +2857,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="133" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
         <v>132</v>
       </c>
@@ -2353,7 +2865,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="134" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
         <v>133</v>
       </c>
@@ -2361,7 +2873,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="135" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
         <v>134</v>
       </c>
@@ -2369,7 +2881,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="136" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
         <v>135</v>
       </c>
@@ -2377,7 +2889,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="137" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
         <v>136</v>
       </c>
@@ -2385,7 +2897,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="138" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
         <v>137</v>
       </c>
@@ -2393,7 +2905,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="139" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
         <v>138</v>
       </c>
@@ -2401,7 +2913,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="140" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
         <v>139</v>
       </c>
@@ -2409,7 +2921,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="141" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
         <v>140</v>
       </c>
@@ -2417,7 +2929,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="142" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
         <v>141</v>
       </c>
@@ -2425,7 +2937,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="143" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
         <v>142</v>
       </c>
@@ -2433,7 +2945,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="144" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
         <v>143</v>
       </c>
@@ -2441,7 +2953,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="145" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A145" t="s">
         <v>144</v>
       </c>
@@ -2449,7 +2961,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="146" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
         <v>145</v>
       </c>
@@ -2457,7 +2969,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="147" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A147" t="s">
         <v>146</v>
       </c>

--- a/.github/tmp_results.xlsx
+++ b/.github/tmp_results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sean Elvidge\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{968A3325-0BEF-459B-AB2F-E5F15E6B0882}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E802B5AA-4A31-4690-A22C-7EB188EF0D11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{156B8CF3-2535-45A6-80D2-358CC30668D6}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="167">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="161">
   <si>
     <t>AFC Bournemouth</t>
   </si>
@@ -501,12 +501,6 @@
     <t>Tier Ch</t>
   </si>
   <si>
-    <t>2-0</t>
-  </si>
-  <si>
-    <t>3-0</t>
-  </si>
-  <si>
     <t>1-1</t>
   </si>
   <si>
@@ -519,25 +513,13 @@
     <t>2-2</t>
   </si>
   <si>
-    <t>1-0</t>
-  </si>
-  <si>
-    <t>2-4</t>
-  </si>
-  <si>
-    <t>0-2</t>
-  </si>
-  <si>
-    <t>3-3</t>
-  </si>
-  <si>
-    <t>1-3</t>
-  </si>
-  <si>
-    <t>0-1</t>
-  </si>
-  <si>
-    <t>1-4</t>
+    <t>4-3</t>
+  </si>
+  <si>
+    <t>4-1</t>
+  </si>
+  <si>
+    <t>2-1</t>
   </si>
 </sst>
 </file>
@@ -945,35 +927,35 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" s="2">
-        <v>46129</v>
+        <v>46131</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="C2" t="s">
-        <v>41</v>
+        <v>126</v>
       </c>
       <c r="D2">
         <f>VLOOKUP(B2,Teams!A:B,2,FALSE)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E2">
         <f>VLOOKUP(C2,Teams!A:B,2,FALSE)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" s="2">
-        <v>46130</v>
+        <v>46131</v>
       </c>
       <c r="B3" t="s">
-        <v>21</v>
+        <v>51</v>
       </c>
       <c r="C3" t="s">
-        <v>55</v>
+        <v>74</v>
       </c>
       <c r="D3">
         <f>VLOOKUP(B3,Teams!A:B,2,FALSE)</f>
@@ -984,18 +966,18 @@
         <v>1</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" s="2">
-        <v>46130</v>
+        <v>46131</v>
       </c>
       <c r="B4" t="s">
-        <v>70</v>
+        <v>96</v>
       </c>
       <c r="C4" t="s">
-        <v>141</v>
+        <v>26</v>
       </c>
       <c r="D4">
         <f>VLOOKUP(B4,Teams!A:B,2,FALSE)</f>
@@ -1006,18 +988,18 @@
         <v>1</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" s="2">
-        <v>46130</v>
+        <v>46131</v>
       </c>
       <c r="B5" t="s">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="C5" t="s">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D5">
         <f>VLOOKUP(B5,Teams!A:B,2,FALSE)</f>
@@ -1028,751 +1010,181 @@
         <v>1</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" s="2">
-        <v>46130</v>
+        <v>46131</v>
       </c>
       <c r="B6" t="s">
-        <v>132</v>
+        <v>67</v>
       </c>
       <c r="C6" t="s">
-        <v>22</v>
+        <v>83</v>
       </c>
       <c r="D6">
         <f>VLOOKUP(B6,Teams!A:B,2,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E6">
         <f>VLOOKUP(C6,Teams!A:B,2,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" s="2">
-        <v>46130</v>
+        <v>46131</v>
       </c>
       <c r="B7" t="s">
-        <v>36</v>
+        <v>100</v>
       </c>
       <c r="C7" t="s">
-        <v>80</v>
+        <v>27</v>
       </c>
       <c r="D7">
         <f>VLOOKUP(B7,Teams!A:B,2,FALSE)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E7">
         <f>VLOOKUP(C7,Teams!A:B,2,FALSE)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>165</v>
+        <v>154</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" s="2">
-        <v>46130</v>
+        <v>46131</v>
       </c>
       <c r="B8" t="s">
-        <v>48</v>
+        <v>102</v>
       </c>
       <c r="C8" t="s">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="D8">
         <f>VLOOKUP(B8,Teams!A:B,2,FALSE)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E8">
         <f>VLOOKUP(C8,Teams!A:B,2,FALSE)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A9" s="2">
-        <v>46130</v>
-      </c>
-      <c r="B9" t="s">
-        <v>85</v>
-      </c>
-      <c r="C9" t="s">
-        <v>105</v>
-      </c>
-      <c r="D9">
-        <f>VLOOKUP(B9,Teams!A:B,2,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="E9">
-        <f>VLOOKUP(C9,Teams!A:B,2,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>154</v>
-      </c>
+      <c r="A9" s="2"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A10" s="2">
-        <v>46130</v>
-      </c>
-      <c r="B10" t="s">
-        <v>103</v>
-      </c>
-      <c r="C10" t="s">
-        <v>71</v>
-      </c>
-      <c r="D10">
-        <f>VLOOKUP(B10,Teams!A:B,2,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="E10">
-        <f>VLOOKUP(C10,Teams!A:B,2,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>160</v>
-      </c>
+      <c r="A10" s="2"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A11" s="2">
-        <v>46130</v>
-      </c>
-      <c r="B11" t="s">
-        <v>23</v>
-      </c>
-      <c r="C11" t="s">
-        <v>95</v>
-      </c>
-      <c r="D11">
-        <f>VLOOKUP(B11,Teams!A:B,2,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="E11">
-        <f>VLOOKUP(C11,Teams!A:B,2,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>161</v>
-      </c>
+      <c r="A11" s="2"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A12" s="2">
-        <v>46130</v>
-      </c>
-      <c r="B12" t="s">
-        <v>66</v>
-      </c>
-      <c r="C12" t="s">
-        <v>13</v>
-      </c>
-      <c r="D12">
-        <f>VLOOKUP(B12,Teams!A:B,2,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="E12">
-        <f>VLOOKUP(C12,Teams!A:B,2,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>156</v>
-      </c>
+      <c r="A12" s="2"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A13" s="2">
-        <v>46130</v>
-      </c>
-      <c r="B13" t="s">
-        <v>104</v>
-      </c>
-      <c r="C13" t="s">
-        <v>136</v>
-      </c>
-      <c r="D13">
-        <f>VLOOKUP(B13,Teams!A:B,2,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="E13">
-        <f>VLOOKUP(C13,Teams!A:B,2,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>162</v>
-      </c>
+      <c r="A13" s="2"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A14" s="2">
-        <v>46130</v>
-      </c>
-      <c r="B14" t="s">
-        <v>116</v>
-      </c>
-      <c r="C14" t="s">
-        <v>35</v>
-      </c>
-      <c r="D14">
-        <f>VLOOKUP(B14,Teams!A:B,2,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="E14">
-        <f>VLOOKUP(C14,Teams!A:B,2,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>156</v>
-      </c>
+      <c r="A14" s="2"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A15" s="2">
-        <v>46130</v>
-      </c>
-      <c r="B15" t="s">
-        <v>128</v>
-      </c>
-      <c r="C15" t="s">
-        <v>119</v>
-      </c>
-      <c r="D15">
-        <f>VLOOKUP(B15,Teams!A:B,2,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="E15">
-        <f>VLOOKUP(C15,Teams!A:B,2,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>158</v>
-      </c>
+      <c r="A15" s="2"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A16" s="2">
-        <v>46130</v>
-      </c>
-      <c r="B16" t="s">
-        <v>135</v>
-      </c>
-      <c r="C16" t="s">
-        <v>115</v>
-      </c>
-      <c r="D16">
-        <f>VLOOKUP(B16,Teams!A:B,2,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="E16">
-        <f>VLOOKUP(C16,Teams!A:B,2,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="F16" s="3" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A17" s="2">
-        <v>46130</v>
-      </c>
-      <c r="B17" t="s">
-        <v>143</v>
-      </c>
-      <c r="C17" t="s">
-        <v>125</v>
-      </c>
-      <c r="D17">
-        <f>VLOOKUP(B17,Teams!A:B,2,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="E17">
-        <f>VLOOKUP(C17,Teams!A:B,2,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A18" s="2">
-        <v>46130</v>
-      </c>
-      <c r="B18" t="s">
-        <v>11</v>
-      </c>
-      <c r="C18" t="s">
-        <v>19</v>
-      </c>
-      <c r="D18">
-        <f>VLOOKUP(B18,Teams!A:B,2,FALSE)</f>
-        <v>3</v>
-      </c>
-      <c r="E18">
-        <f>VLOOKUP(C18,Teams!A:B,2,FALSE)</f>
-        <v>3</v>
-      </c>
-      <c r="F18" s="3" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A19" s="2">
-        <v>46130</v>
-      </c>
-      <c r="B19" t="s">
-        <v>16</v>
-      </c>
-      <c r="C19" t="s">
-        <v>65</v>
-      </c>
-      <c r="D19">
-        <f>VLOOKUP(B19,Teams!A:B,2,FALSE)</f>
-        <v>3</v>
-      </c>
-      <c r="E19">
-        <f>VLOOKUP(C19,Teams!A:B,2,FALSE)</f>
-        <v>3</v>
-      </c>
-      <c r="F19" s="3" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A20" s="2">
-        <v>46130</v>
-      </c>
-      <c r="B20" t="s">
-        <v>1</v>
-      </c>
-      <c r="C20" t="s">
-        <v>101</v>
-      </c>
-      <c r="D20">
-        <f>VLOOKUP(B20,Teams!A:B,2,FALSE)</f>
-        <v>3</v>
-      </c>
-      <c r="E20">
-        <f>VLOOKUP(C20,Teams!A:B,2,FALSE)</f>
-        <v>3</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A21" s="2">
-        <v>46130</v>
-      </c>
-      <c r="B21" t="s">
-        <v>52</v>
-      </c>
-      <c r="C21" t="s">
-        <v>124</v>
-      </c>
-      <c r="D21">
-        <f>VLOOKUP(B21,Teams!A:B,2,FALSE)</f>
-        <v>3</v>
-      </c>
-      <c r="E21">
-        <f>VLOOKUP(C21,Teams!A:B,2,FALSE)</f>
-        <v>3</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A22" s="2">
-        <v>46130</v>
-      </c>
-      <c r="B22" t="s">
-        <v>72</v>
-      </c>
-      <c r="C22" t="s">
-        <v>110</v>
-      </c>
-      <c r="D22">
-        <f>VLOOKUP(B22,Teams!A:B,2,FALSE)</f>
-        <v>3</v>
-      </c>
-      <c r="E22">
-        <f>VLOOKUP(C22,Teams!A:B,2,FALSE)</f>
-        <v>3</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A23" s="2">
-        <v>46130</v>
-      </c>
-      <c r="B23" t="s">
-        <v>81</v>
-      </c>
-      <c r="C23" t="s">
-        <v>76</v>
-      </c>
-      <c r="D23">
-        <f>VLOOKUP(B23,Teams!A:B,2,FALSE)</f>
-        <v>3</v>
-      </c>
-      <c r="E23">
-        <f>VLOOKUP(C23,Teams!A:B,2,FALSE)</f>
-        <v>3</v>
-      </c>
-      <c r="F23" s="3" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A24" s="2">
-        <v>46130</v>
-      </c>
-      <c r="B24" t="s">
-        <v>93</v>
-      </c>
-      <c r="C24" t="s">
-        <v>49</v>
-      </c>
-      <c r="D24">
-        <f>VLOOKUP(B24,Teams!A:B,2,FALSE)</f>
-        <v>3</v>
-      </c>
-      <c r="E24">
-        <f>VLOOKUP(C24,Teams!A:B,2,FALSE)</f>
-        <v>3</v>
-      </c>
-      <c r="F24" s="3" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A25" s="2">
-        <v>46130</v>
-      </c>
-      <c r="B25" t="s">
-        <v>106</v>
-      </c>
-      <c r="C25" t="s">
-        <v>33</v>
-      </c>
-      <c r="D25">
-        <f>VLOOKUP(B25,Teams!A:B,2,FALSE)</f>
-        <v>3</v>
-      </c>
-      <c r="E25">
-        <f>VLOOKUP(C25,Teams!A:B,2,FALSE)</f>
-        <v>3</v>
-      </c>
-      <c r="F25" s="3" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A26" s="2">
-        <v>46130</v>
-      </c>
-      <c r="B26" t="s">
-        <v>123</v>
-      </c>
-      <c r="C26" t="s">
-        <v>73</v>
-      </c>
-      <c r="D26">
-        <f>VLOOKUP(B26,Teams!A:B,2,FALSE)</f>
-        <v>3</v>
-      </c>
-      <c r="E26">
-        <f>VLOOKUP(C26,Teams!A:B,2,FALSE)</f>
-        <v>3</v>
-      </c>
-      <c r="F26" s="3" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A27" s="2">
-        <v>46130</v>
-      </c>
-      <c r="B27" t="s">
-        <v>144</v>
-      </c>
-      <c r="C27" t="s">
-        <v>15</v>
-      </c>
-      <c r="D27">
-        <f>VLOOKUP(B27,Teams!A:B,2,FALSE)</f>
-        <v>3</v>
-      </c>
-      <c r="E27">
-        <f>VLOOKUP(C27,Teams!A:B,2,FALSE)</f>
-        <v>3</v>
-      </c>
-      <c r="F27" s="3" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A28" s="2">
-        <v>46130</v>
-      </c>
-      <c r="B28" t="s">
-        <v>12</v>
-      </c>
-      <c r="C28" t="s">
-        <v>134</v>
-      </c>
-      <c r="D28">
-        <f>VLOOKUP(B28,Teams!A:B,2,FALSE)</f>
-        <v>4</v>
-      </c>
-      <c r="E28">
-        <f>VLOOKUP(C28,Teams!A:B,2,FALSE)</f>
-        <v>4</v>
-      </c>
-      <c r="F28" s="3" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A29" s="2">
-        <v>46130</v>
-      </c>
-      <c r="B29" t="s">
-        <v>129</v>
-      </c>
-      <c r="C29" t="s">
-        <v>4</v>
-      </c>
-      <c r="D29">
-        <f>VLOOKUP(B29,Teams!A:B,2,FALSE)</f>
-        <v>4</v>
-      </c>
-      <c r="E29">
-        <f>VLOOKUP(C29,Teams!A:B,2,FALSE)</f>
-        <v>4</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A30" s="2">
-        <v>46130</v>
-      </c>
-      <c r="B30" t="s">
-        <v>37</v>
-      </c>
-      <c r="C30" t="s">
-        <v>92</v>
-      </c>
-      <c r="D30">
-        <f>VLOOKUP(B30,Teams!A:B,2,FALSE)</f>
-        <v>4</v>
-      </c>
-      <c r="E30">
-        <f>VLOOKUP(C30,Teams!A:B,2,FALSE)</f>
-        <v>4</v>
-      </c>
-      <c r="F30" s="3" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A31" s="2">
-        <v>46130</v>
-      </c>
-      <c r="B31" t="s">
-        <v>42</v>
-      </c>
-      <c r="C31" t="s">
-        <v>117</v>
-      </c>
-      <c r="D31">
-        <f>VLOOKUP(B31,Teams!A:B,2,FALSE)</f>
-        <v>4</v>
-      </c>
-      <c r="E31">
-        <f>VLOOKUP(C31,Teams!A:B,2,FALSE)</f>
-        <v>4</v>
-      </c>
-      <c r="F31" s="3" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A32" s="2">
-        <v>46130</v>
-      </c>
-      <c r="B32" t="s">
-        <v>43</v>
-      </c>
-      <c r="C32" t="s">
-        <v>86</v>
-      </c>
-      <c r="D32">
-        <f>VLOOKUP(B32,Teams!A:B,2,FALSE)</f>
-        <v>4</v>
-      </c>
-      <c r="E32">
-        <f>VLOOKUP(C32,Teams!A:B,2,FALSE)</f>
-        <v>4</v>
-      </c>
-      <c r="F32" s="3" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A33" s="2">
-        <v>46130</v>
-      </c>
-      <c r="B33" t="s">
-        <v>53</v>
-      </c>
-      <c r="C33" t="s">
-        <v>39</v>
-      </c>
-      <c r="D33">
-        <f>VLOOKUP(B33,Teams!A:B,2,FALSE)</f>
-        <v>4</v>
-      </c>
-      <c r="E33">
-        <f>VLOOKUP(C33,Teams!A:B,2,FALSE)</f>
-        <v>4</v>
-      </c>
-      <c r="F33" s="3" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A34" s="2">
-        <v>46130</v>
-      </c>
-      <c r="B34" t="s">
-        <v>58</v>
-      </c>
-      <c r="C34" t="s">
-        <v>60</v>
-      </c>
-      <c r="D34">
-        <f>VLOOKUP(B34,Teams!A:B,2,FALSE)</f>
-        <v>4</v>
-      </c>
-      <c r="E34">
-        <f>VLOOKUP(C34,Teams!A:B,2,FALSE)</f>
-        <v>4</v>
-      </c>
-      <c r="F34" s="3" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A35" s="2">
-        <v>46130</v>
-      </c>
-      <c r="B35" t="s">
-        <v>62</v>
-      </c>
-      <c r="C35" t="s">
-        <v>40</v>
-      </c>
-      <c r="D35">
-        <f>VLOOKUP(B35,Teams!A:B,2,FALSE)</f>
-        <v>4</v>
-      </c>
-      <c r="E35">
-        <f>VLOOKUP(C35,Teams!A:B,2,FALSE)</f>
-        <v>4</v>
-      </c>
-      <c r="F35" s="3" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A36" s="2">
-        <v>46130</v>
-      </c>
-      <c r="B36" t="s">
-        <v>97</v>
-      </c>
-      <c r="C36" t="s">
-        <v>10</v>
-      </c>
-      <c r="D36">
-        <f>VLOOKUP(B36,Teams!A:B,2,FALSE)</f>
-        <v>4</v>
-      </c>
-      <c r="E36">
-        <f>VLOOKUP(C36,Teams!A:B,2,FALSE)</f>
-        <v>4</v>
-      </c>
-      <c r="F36" s="3" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A37" s="2">
-        <v>46130</v>
-      </c>
-      <c r="B37" t="s">
-        <v>98</v>
-      </c>
-      <c r="C37" t="s">
-        <v>112</v>
-      </c>
-      <c r="D37">
-        <f>VLOOKUP(B37,Teams!A:B,2,FALSE)</f>
-        <v>4</v>
-      </c>
-      <c r="E37">
-        <f>VLOOKUP(C37,Teams!A:B,2,FALSE)</f>
-        <v>4</v>
-      </c>
-      <c r="F37" s="3" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A38" s="2">
-        <v>46130</v>
-      </c>
-      <c r="B38" t="s">
-        <v>133</v>
-      </c>
-      <c r="C38" t="s">
-        <v>24</v>
-      </c>
-      <c r="D38">
-        <f>VLOOKUP(B38,Teams!A:B,2,FALSE)</f>
-        <v>4</v>
-      </c>
-      <c r="E38">
-        <f>VLOOKUP(C38,Teams!A:B,2,FALSE)</f>
-        <v>4</v>
-      </c>
-      <c r="F38" s="3" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A16" s="2"/>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A17" s="2"/>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A18" s="2"/>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A19" s="2"/>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A20" s="2"/>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A21" s="2"/>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A22" s="2"/>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A23" s="2"/>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A24" s="2"/>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A25" s="2"/>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A26" s="2"/>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A27" s="2"/>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A28" s="2"/>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A29" s="2"/>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A30" s="2"/>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A31" s="2"/>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A32" s="2"/>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A33" s="2"/>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A34" s="2"/>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A35" s="2"/>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A36" s="2"/>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A37" s="2"/>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A38" s="2"/>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A39" s="2"/>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A40" s="2"/>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A41" s="2"/>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A42" s="2"/>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A43" s="2"/>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A44" s="2"/>
     </row>
   </sheetData>

--- a/.github/tmp_results.xlsx
+++ b/.github/tmp_results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sean Elvidge\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E802B5AA-4A31-4690-A22C-7EB188EF0D11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A827E73-2FF8-4D37-86DC-E4206B9E87B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{156B8CF3-2535-45A6-80D2-358CC30668D6}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="155">
   <si>
     <t>AFC Bournemouth</t>
   </si>
@@ -501,25 +501,7 @@
     <t>Tier Ch</t>
   </si>
   <si>
-    <t>1-1</t>
-  </si>
-  <si>
     <t>0-0</t>
-  </si>
-  <si>
-    <t>1-2</t>
-  </si>
-  <si>
-    <t>2-2</t>
-  </si>
-  <si>
-    <t>4-3</t>
-  </si>
-  <si>
-    <t>4-1</t>
-  </si>
-  <si>
-    <t>2-1</t>
   </si>
 </sst>
 </file>
@@ -927,13 +909,13 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" s="2">
-        <v>46131</v>
+        <v>46132</v>
       </c>
       <c r="B2" t="s">
-        <v>9</v>
+        <v>44</v>
       </c>
       <c r="C2" t="s">
-        <v>126</v>
+        <v>137</v>
       </c>
       <c r="D2">
         <f>VLOOKUP(B2,Teams!A:B,2,FALSE)</f>
@@ -944,140 +926,26 @@
         <v>1</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A3" s="2">
-        <v>46131</v>
-      </c>
-      <c r="B3" t="s">
-        <v>51</v>
-      </c>
-      <c r="C3" t="s">
-        <v>74</v>
-      </c>
-      <c r="D3">
-        <f>VLOOKUP(B3,Teams!A:B,2,FALSE)</f>
-        <v>1</v>
-      </c>
-      <c r="E3">
-        <f>VLOOKUP(C3,Teams!A:B,2,FALSE)</f>
-        <v>1</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>156</v>
-      </c>
+      <c r="A3" s="2"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A4" s="2">
-        <v>46131</v>
-      </c>
-      <c r="B4" t="s">
-        <v>96</v>
-      </c>
-      <c r="C4" t="s">
-        <v>26</v>
-      </c>
-      <c r="D4">
-        <f>VLOOKUP(B4,Teams!A:B,2,FALSE)</f>
-        <v>1</v>
-      </c>
-      <c r="E4">
-        <f>VLOOKUP(C4,Teams!A:B,2,FALSE)</f>
-        <v>1</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>159</v>
-      </c>
+      <c r="A4" s="2"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A5" s="2">
-        <v>46131</v>
-      </c>
-      <c r="B5" t="s">
-        <v>79</v>
-      </c>
-      <c r="C5" t="s">
-        <v>7</v>
-      </c>
-      <c r="D5">
-        <f>VLOOKUP(B5,Teams!A:B,2,FALSE)</f>
-        <v>1</v>
-      </c>
-      <c r="E5">
-        <f>VLOOKUP(C5,Teams!A:B,2,FALSE)</f>
-        <v>1</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>160</v>
-      </c>
+      <c r="A5" s="2"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A6" s="2">
-        <v>46131</v>
-      </c>
-      <c r="B6" t="s">
-        <v>67</v>
-      </c>
-      <c r="C6" t="s">
-        <v>83</v>
-      </c>
-      <c r="D6">
-        <f>VLOOKUP(B6,Teams!A:B,2,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="E6">
-        <f>VLOOKUP(C6,Teams!A:B,2,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>157</v>
-      </c>
+      <c r="A6" s="2"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A7" s="2">
-        <v>46131</v>
-      </c>
-      <c r="B7" t="s">
-        <v>100</v>
-      </c>
-      <c r="C7" t="s">
-        <v>27</v>
-      </c>
-      <c r="D7">
-        <f>VLOOKUP(B7,Teams!A:B,2,FALSE)</f>
-        <v>3</v>
-      </c>
-      <c r="E7">
-        <f>VLOOKUP(C7,Teams!A:B,2,FALSE)</f>
-        <v>3</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>154</v>
-      </c>
+      <c r="A7" s="2"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A8" s="2">
-        <v>46131</v>
-      </c>
-      <c r="B8" t="s">
-        <v>102</v>
-      </c>
-      <c r="C8" t="s">
-        <v>138</v>
-      </c>
-      <c r="D8">
-        <f>VLOOKUP(B8,Teams!A:B,2,FALSE)</f>
-        <v>3</v>
-      </c>
-      <c r="E8">
-        <f>VLOOKUP(C8,Teams!A:B,2,FALSE)</f>
-        <v>3</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>155</v>
-      </c>
+      <c r="A8" s="2"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" s="2"/>

--- a/.github/tmp_results.xlsx
+++ b/.github/tmp_results.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sean Elvidge\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\elvidgsm\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A827E73-2FF8-4D37-86DC-E4206B9E87B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91CCB27C-522C-4F51-9D09-27048C538EF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{156B8CF3-2535-45A6-80D2-358CC30668D6}"/>
+    <workbookView xWindow="23460" yWindow="2340" windowWidth="25755" windowHeight="15345" xr2:uid="{156B8CF3-2535-45A6-80D2-358CC30668D6}"/>
   </bookViews>
   <sheets>
     <sheet name="Scores" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="164">
   <si>
     <t>AFC Bournemouth</t>
   </si>
@@ -501,7 +501,34 @@
     <t>Tier Ch</t>
   </si>
   <si>
-    <t>0-0</t>
+    <t>3-0</t>
+  </si>
+  <si>
+    <t>5-1</t>
+  </si>
+  <si>
+    <t>2-2</t>
+  </si>
+  <si>
+    <t>2-1</t>
+  </si>
+  <si>
+    <t>0-1</t>
+  </si>
+  <si>
+    <t>1-2</t>
+  </si>
+  <si>
+    <t>1-3</t>
+  </si>
+  <si>
+    <t>1-1</t>
+  </si>
+  <si>
+    <t>0-2</t>
+  </si>
+  <si>
+    <t>1-0</t>
   </si>
 </sst>
 </file>
@@ -879,15 +906,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{944D37C4-CAD2-4526-8947-361FF9BC37B9}">
   <dimension ref="A1:F44"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.54296875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.81640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.85546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="23" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.7265625" style="3"/>
+    <col min="6" max="6" width="8.7109375" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>149</v>
       </c>
@@ -907,15 +934,15 @@
         <v>152</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B2" t="s">
-        <v>44</v>
+        <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>137</v>
+        <v>36</v>
       </c>
       <c r="D2">
         <f>VLOOKUP(B2,Teams!A:B,2,FALSE)</f>
@@ -929,130 +956,548 @@
         <v>154</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A3" s="2"/>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A4" s="2"/>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A5" s="2"/>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A6" s="2"/>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A7" s="2"/>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A8" s="2"/>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A9" s="2"/>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A10" s="2"/>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A11" s="2"/>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A12" s="2"/>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A13" s="2"/>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A14" s="2"/>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A15" s="2"/>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A16" s="2"/>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A17" s="2"/>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A18" s="2"/>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A19" s="2"/>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A20" s="2"/>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A21" s="2"/>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A22" s="2"/>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A23" s="2"/>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A24" s="2"/>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="2">
+        <v>46133</v>
+      </c>
+      <c r="B3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C3" t="s">
+        <v>103</v>
+      </c>
+      <c r="D3">
+        <f>VLOOKUP(B3,Teams!A:B,2,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="E3">
+        <f>VLOOKUP(C3,Teams!A:B,2,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="2">
+        <v>46133</v>
+      </c>
+      <c r="B4" t="s">
+        <v>71</v>
+      </c>
+      <c r="C4" t="s">
+        <v>66</v>
+      </c>
+      <c r="D4">
+        <f>VLOOKUP(B4,Teams!A:B,2,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="E4">
+        <f>VLOOKUP(C4,Teams!A:B,2,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="2">
+        <v>46133</v>
+      </c>
+      <c r="B5" t="s">
+        <v>95</v>
+      </c>
+      <c r="C5" t="s">
+        <v>48</v>
+      </c>
+      <c r="D5">
+        <f>VLOOKUP(B5,Teams!A:B,2,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="E5">
+        <f>VLOOKUP(C5,Teams!A:B,2,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="2">
+        <v>46133</v>
+      </c>
+      <c r="B6" t="s">
+        <v>99</v>
+      </c>
+      <c r="C6" t="s">
+        <v>143</v>
+      </c>
+      <c r="D6">
+        <f>VLOOKUP(B6,Teams!A:B,2,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="E6">
+        <f>VLOOKUP(C6,Teams!A:B,2,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="2">
+        <v>46133</v>
+      </c>
+      <c r="B7" t="s">
+        <v>105</v>
+      </c>
+      <c r="C7" t="s">
+        <v>128</v>
+      </c>
+      <c r="D7">
+        <f>VLOOKUP(B7,Teams!A:B,2,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="E7">
+        <f>VLOOKUP(C7,Teams!A:B,2,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="2">
+        <v>46133</v>
+      </c>
+      <c r="B8" t="s">
+        <v>119</v>
+      </c>
+      <c r="C8" t="s">
+        <v>23</v>
+      </c>
+      <c r="D8">
+        <f>VLOOKUP(B8,Teams!A:B,2,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="E8">
+        <f>VLOOKUP(C8,Teams!A:B,2,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="2">
+        <v>46133</v>
+      </c>
+      <c r="B9" t="s">
+        <v>125</v>
+      </c>
+      <c r="C9" t="s">
+        <v>85</v>
+      </c>
+      <c r="D9">
+        <f>VLOOKUP(B9,Teams!A:B,2,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="E9">
+        <f>VLOOKUP(C9,Teams!A:B,2,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="2">
+        <v>46133</v>
+      </c>
+      <c r="B10" t="s">
+        <v>136</v>
+      </c>
+      <c r="C10" t="s">
+        <v>135</v>
+      </c>
+      <c r="D10">
+        <f>VLOOKUP(B10,Teams!A:B,2,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="E10">
+        <f>VLOOKUP(C10,Teams!A:B,2,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="2">
+        <v>46133</v>
+      </c>
+      <c r="B11" t="s">
+        <v>19</v>
+      </c>
+      <c r="C11" t="s">
+        <v>101</v>
+      </c>
+      <c r="D11">
+        <f>VLOOKUP(B11,Teams!A:B,2,FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="E11">
+        <f>VLOOKUP(C11,Teams!A:B,2,FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="2">
+        <v>46133</v>
+      </c>
+      <c r="B12" t="s">
+        <v>49</v>
+      </c>
+      <c r="C12" t="s">
+        <v>73</v>
+      </c>
+      <c r="D12">
+        <f>VLOOKUP(B12,Teams!A:B,2,FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="E12">
+        <f>VLOOKUP(C12,Teams!A:B,2,FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="2">
+        <v>46133</v>
+      </c>
+      <c r="B13" t="s">
+        <v>110</v>
+      </c>
+      <c r="C13" t="s">
+        <v>76</v>
+      </c>
+      <c r="D13">
+        <f>VLOOKUP(B13,Teams!A:B,2,FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="E13">
+        <f>VLOOKUP(C13,Teams!A:B,2,FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="2">
+        <v>46133</v>
+      </c>
+      <c r="B14" t="s">
+        <v>123</v>
+      </c>
+      <c r="C14" t="s">
+        <v>11</v>
+      </c>
+      <c r="D14">
+        <f>VLOOKUP(B14,Teams!A:B,2,FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="E14">
+        <f>VLOOKUP(C14,Teams!A:B,2,FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="2">
+        <v>46133</v>
+      </c>
+      <c r="B15" t="s">
+        <v>124</v>
+      </c>
+      <c r="C15" t="s">
+        <v>81</v>
+      </c>
+      <c r="D15">
+        <f>VLOOKUP(B15,Teams!A:B,2,FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="E15">
+        <f>VLOOKUP(C15,Teams!A:B,2,FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="2">
+        <v>46133</v>
+      </c>
+      <c r="B16" t="s">
+        <v>32</v>
+      </c>
+      <c r="C16" t="s">
+        <v>60</v>
+      </c>
+      <c r="D16">
+        <f>VLOOKUP(B16,Teams!A:B,2,FALSE)</f>
+        <v>4</v>
+      </c>
+      <c r="E16">
+        <f>VLOOKUP(C16,Teams!A:B,2,FALSE)</f>
+        <v>4</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="2">
+        <v>46133</v>
+      </c>
+      <c r="B17" t="s">
+        <v>37</v>
+      </c>
+      <c r="C17" t="s">
+        <v>133</v>
+      </c>
+      <c r="D17">
+        <f>VLOOKUP(B17,Teams!A:B,2,FALSE)</f>
+        <v>4</v>
+      </c>
+      <c r="E17">
+        <f>VLOOKUP(C17,Teams!A:B,2,FALSE)</f>
+        <v>4</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="2">
+        <v>46134</v>
+      </c>
+      <c r="B18" t="s">
+        <v>0</v>
+      </c>
+      <c r="C18" t="s">
+        <v>70</v>
+      </c>
+      <c r="D18">
+        <f>VLOOKUP(B18,Teams!A:B,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="E18">
+        <f>VLOOKUP(C18,Teams!A:B,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="2">
+        <v>46134</v>
+      </c>
+      <c r="B19" t="s">
+        <v>26</v>
+      </c>
+      <c r="C19" t="s">
+        <v>79</v>
+      </c>
+      <c r="D19">
+        <f>VLOOKUP(B19,Teams!A:B,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="E19">
+        <f>VLOOKUP(C19,Teams!A:B,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="2">
+        <v>46134</v>
+      </c>
+      <c r="B20" t="s">
+        <v>13</v>
+      </c>
+      <c r="C20" t="s">
+        <v>104</v>
+      </c>
+      <c r="D20">
+        <f>VLOOKUP(B20,Teams!A:B,2,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="E20">
+        <f>VLOOKUP(C20,Teams!A:B,2,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="2">
+        <v>46134</v>
+      </c>
+      <c r="B21" t="s">
+        <v>35</v>
+      </c>
+      <c r="C21" t="s">
+        <v>67</v>
+      </c>
+      <c r="D21">
+        <f>VLOOKUP(B21,Teams!A:B,2,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="E21">
+        <f>VLOOKUP(C21,Teams!A:B,2,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="2">
+        <v>46134</v>
+      </c>
+      <c r="B22" t="s">
+        <v>83</v>
+      </c>
+      <c r="C22" t="s">
+        <v>116</v>
+      </c>
+      <c r="D22">
+        <f>VLOOKUP(B22,Teams!A:B,2,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="E22">
+        <f>VLOOKUP(C22,Teams!A:B,2,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="2">
+        <v>46134</v>
+      </c>
+      <c r="B23" t="s">
+        <v>115</v>
+      </c>
+      <c r="C23" t="s">
+        <v>14</v>
+      </c>
+      <c r="D23">
+        <f>VLOOKUP(B23,Teams!A:B,2,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="E23">
+        <f>VLOOKUP(C23,Teams!A:B,2,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="2">
+        <v>46134</v>
+      </c>
+      <c r="B24" t="s">
+        <v>33</v>
+      </c>
+      <c r="C24" t="s">
+        <v>102</v>
+      </c>
+      <c r="D24">
+        <f>VLOOKUP(B24,Teams!A:B,2,FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="E24">
+        <f>VLOOKUP(C24,Teams!A:B,2,FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="2"/>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="2"/>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="2"/>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="2"/>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="2"/>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="2"/>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="2"/>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="2"/>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" s="2"/>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" s="2"/>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" s="2"/>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" s="2"/>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" s="2"/>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" s="2"/>
     </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" s="2"/>
     </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" s="2"/>
     </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" s="2"/>
     </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A42" s="2"/>
     </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A43" s="2"/>
     </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A44" s="2"/>
     </row>
   </sheetData>
@@ -1075,13 +1520,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{660D5CBD-EF61-4F28-8F5F-C3B953B1D14A}">
   <dimension ref="A1:B147"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="23" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.7265625" style="1"/>
+    <col min="2" max="2" width="8.7109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1089,7 +1534,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -1097,7 +1542,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -1105,7 +1550,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1113,7 +1558,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -1121,7 +1566,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -1129,7 +1574,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -1137,7 +1582,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -1145,7 +1590,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>8</v>
       </c>
@@ -1153,7 +1598,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>9</v>
       </c>
@@ -1161,7 +1606,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>10</v>
       </c>
@@ -1169,7 +1614,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>11</v>
       </c>
@@ -1177,7 +1622,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>12</v>
       </c>
@@ -1185,7 +1630,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>13</v>
       </c>
@@ -1193,7 +1638,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>14</v>
       </c>
@@ -1201,7 +1646,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>15</v>
       </c>
@@ -1209,7 +1654,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>16</v>
       </c>
@@ -1217,7 +1662,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>17</v>
       </c>
@@ -1225,7 +1670,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>18</v>
       </c>
@@ -1233,7 +1678,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>19</v>
       </c>
@@ -1241,7 +1686,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>20</v>
       </c>
@@ -1249,7 +1694,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>21</v>
       </c>
@@ -1257,7 +1702,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>22</v>
       </c>
@@ -1265,7 +1710,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>23</v>
       </c>
@@ -1273,7 +1718,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>24</v>
       </c>
@@ -1281,7 +1726,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>25</v>
       </c>
@@ -1289,7 +1734,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>26</v>
       </c>
@@ -1297,7 +1742,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>27</v>
       </c>
@@ -1305,7 +1750,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>28</v>
       </c>
@@ -1313,7 +1758,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>29</v>
       </c>
@@ -1321,7 +1766,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>30</v>
       </c>
@@ -1329,7 +1774,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>31</v>
       </c>
@@ -1337,7 +1782,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>32</v>
       </c>
@@ -1345,7 +1790,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>33</v>
       </c>
@@ -1353,7 +1798,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>34</v>
       </c>
@@ -1361,7 +1806,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>35</v>
       </c>
@@ -1369,7 +1814,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>36</v>
       </c>
@@ -1377,7 +1822,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>37</v>
       </c>
@@ -1385,7 +1830,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>38</v>
       </c>
@@ -1393,7 +1838,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>39</v>
       </c>
@@ -1401,7 +1846,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>40</v>
       </c>
@@ -1409,7 +1854,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>41</v>
       </c>
@@ -1417,7 +1862,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>42</v>
       </c>
@@ -1425,7 +1870,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>43</v>
       </c>
@@ -1433,7 +1878,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>44</v>
       </c>
@@ -1441,7 +1886,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>45</v>
       </c>
@@ -1449,7 +1894,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>46</v>
       </c>
@@ -1457,7 +1902,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>47</v>
       </c>
@@ -1465,7 +1910,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>48</v>
       </c>
@@ -1473,7 +1918,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>49</v>
       </c>
@@ -1481,7 +1926,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>50</v>
       </c>
@@ -1489,7 +1934,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>51</v>
       </c>
@@ -1497,7 +1942,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>52</v>
       </c>
@@ -1505,7 +1950,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>53</v>
       </c>
@@ -1513,7 +1958,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>54</v>
       </c>
@@ -1521,7 +1966,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>55</v>
       </c>
@@ -1529,7 +1974,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>56</v>
       </c>
@@ -1537,7 +1982,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>57</v>
       </c>
@@ -1545,7 +1990,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>58</v>
       </c>
@@ -1553,7 +1998,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>59</v>
       </c>
@@ -1561,7 +2006,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>60</v>
       </c>
@@ -1569,7 +2014,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>61</v>
       </c>
@@ -1577,7 +2022,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>62</v>
       </c>
@@ -1585,7 +2030,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>63</v>
       </c>
@@ -1593,7 +2038,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>64</v>
       </c>
@@ -1601,7 +2046,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>65</v>
       </c>
@@ -1609,7 +2054,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>66</v>
       </c>
@@ -1617,7 +2062,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>67</v>
       </c>
@@ -1625,7 +2070,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>68</v>
       </c>
@@ -1633,7 +2078,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>69</v>
       </c>
@@ -1641,7 +2086,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>70</v>
       </c>
@@ -1649,7 +2094,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>71</v>
       </c>
@@ -1657,7 +2102,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>72</v>
       </c>
@@ -1665,7 +2110,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>73</v>
       </c>
@@ -1673,7 +2118,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>74</v>
       </c>
@@ -1681,7 +2126,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>75</v>
       </c>
@@ -1689,7 +2134,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>76</v>
       </c>
@@ -1697,7 +2142,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>77</v>
       </c>
@@ -1705,7 +2150,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>78</v>
       </c>
@@ -1713,7 +2158,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>79</v>
       </c>
@@ -1721,7 +2166,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>80</v>
       </c>
@@ -1729,7 +2174,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>81</v>
       </c>
@@ -1737,7 +2182,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>82</v>
       </c>
@@ -1745,7 +2190,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>83</v>
       </c>
@@ -1753,7 +2198,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>84</v>
       </c>
@@ -1761,7 +2206,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>85</v>
       </c>
@@ -1769,7 +2214,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>86</v>
       </c>
@@ -1777,7 +2222,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>87</v>
       </c>
@@ -1785,7 +2230,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>88</v>
       </c>
@@ -1793,7 +2238,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>89</v>
       </c>
@@ -1801,7 +2246,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>90</v>
       </c>
@@ -1809,7 +2254,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>91</v>
       </c>
@@ -1817,7 +2262,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>92</v>
       </c>
@@ -1825,7 +2270,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>93</v>
       </c>
@@ -1833,7 +2278,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>94</v>
       </c>
@@ -1841,7 +2286,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>95</v>
       </c>
@@ -1849,7 +2294,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>96</v>
       </c>
@@ -1857,7 +2302,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>97</v>
       </c>
@@ -1865,7 +2310,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>98</v>
       </c>
@@ -1873,7 +2318,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>99</v>
       </c>
@@ -1881,7 +2326,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>100</v>
       </c>
@@ -1889,7 +2334,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="102" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>101</v>
       </c>
@@ -1897,7 +2342,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="103" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>102</v>
       </c>
@@ -1905,7 +2350,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="104" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>103</v>
       </c>
@@ -1913,7 +2358,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="105" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>104</v>
       </c>
@@ -1921,7 +2366,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="106" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>105</v>
       </c>
@@ -1929,7 +2374,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="107" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>106</v>
       </c>
@@ -1937,7 +2382,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="108" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>107</v>
       </c>
@@ -1945,7 +2390,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="109" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>108</v>
       </c>
@@ -1953,7 +2398,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="110" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>109</v>
       </c>
@@ -1961,7 +2406,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="111" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>110</v>
       </c>
@@ -1969,7 +2414,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="112" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>111</v>
       </c>
@@ -1977,7 +2422,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="113" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>112</v>
       </c>
@@ -1985,7 +2430,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="114" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>113</v>
       </c>
@@ -1993,7 +2438,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="115" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>114</v>
       </c>
@@ -2001,7 +2446,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="116" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>115</v>
       </c>
@@ -2009,7 +2454,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="117" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>116</v>
       </c>
@@ -2017,7 +2462,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="118" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>117</v>
       </c>
@@ -2025,7 +2470,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="119" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>118</v>
       </c>
@@ -2033,7 +2478,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="120" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>119</v>
       </c>
@@ -2041,7 +2486,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="121" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>120</v>
       </c>
@@ -2049,7 +2494,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="122" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>121</v>
       </c>
@@ -2057,7 +2502,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="123" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>122</v>
       </c>
@@ -2065,7 +2510,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="124" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>123</v>
       </c>
@@ -2073,7 +2518,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="125" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>124</v>
       </c>
@@ -2081,7 +2526,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="126" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>125</v>
       </c>
@@ -2089,7 +2534,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="127" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>126</v>
       </c>
@@ -2097,7 +2542,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="128" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>127</v>
       </c>
@@ -2105,7 +2550,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="129" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>128</v>
       </c>
@@ -2113,7 +2558,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="130" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>129</v>
       </c>
@@ -2121,7 +2566,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="131" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>130</v>
       </c>
@@ -2129,7 +2574,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="132" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>131</v>
       </c>
@@ -2137,7 +2582,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="133" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>132</v>
       </c>
@@ -2145,7 +2590,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="134" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>133</v>
       </c>
@@ -2153,7 +2598,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="135" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>134</v>
       </c>
@@ -2161,7 +2606,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="136" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>135</v>
       </c>
@@ -2169,7 +2614,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="137" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>136</v>
       </c>
@@ -2177,7 +2622,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="138" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>137</v>
       </c>
@@ -2185,7 +2630,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="139" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>138</v>
       </c>
@@ -2193,7 +2638,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="140" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>139</v>
       </c>
@@ -2201,7 +2646,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="141" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>140</v>
       </c>
@@ -2209,7 +2654,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="142" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>141</v>
       </c>
@@ -2217,7 +2662,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="143" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>142</v>
       </c>
@@ -2225,7 +2670,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="144" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>143</v>
       </c>
@@ -2233,7 +2678,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="145" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>144</v>
       </c>
@@ -2241,7 +2686,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="146" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>145</v>
       </c>
@@ -2249,7 +2694,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="147" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>146</v>
       </c>

--- a/.github/tmp_results.xlsx
+++ b/.github/tmp_results.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\elvidgsm\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sean Elvidge\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91CCB27C-522C-4F51-9D09-27048C538EF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A214FFC0-653A-4591-A828-CBC67DA4E04B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="23460" yWindow="2340" windowWidth="25755" windowHeight="15345" xr2:uid="{156B8CF3-2535-45A6-80D2-358CC30668D6}"/>
+    <workbookView xWindow="20" yWindow="740" windowWidth="19180" windowHeight="11260" xr2:uid="{156B8CF3-2535-45A6-80D2-358CC30668D6}"/>
   </bookViews>
   <sheets>
     <sheet name="Scores" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="156">
   <si>
     <t>AFC Bournemouth</t>
   </si>
@@ -501,34 +501,10 @@
     <t>Tier Ch</t>
   </si>
   <si>
-    <t>3-0</t>
-  </si>
-  <si>
-    <t>5-1</t>
-  </si>
-  <si>
-    <t>2-2</t>
-  </si>
-  <si>
-    <t>2-1</t>
-  </si>
-  <si>
-    <t>0-1</t>
-  </si>
-  <si>
-    <t>1-2</t>
-  </si>
-  <si>
-    <t>1-3</t>
-  </si>
-  <si>
     <t>1-1</t>
   </si>
   <si>
-    <t>0-2</t>
-  </si>
-  <si>
-    <t>1-0</t>
+    <t>0-5</t>
   </si>
 </sst>
 </file>
@@ -906,15 +882,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{944D37C4-CAD2-4526-8947-361FF9BC37B9}">
   <dimension ref="A1:F44"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.81640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="23" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.7109375" style="3"/>
+    <col min="6" max="6" width="8.7265625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>149</v>
       </c>
@@ -934,15 +910,15 @@
         <v>152</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" s="2">
-        <v>46133</v>
+        <v>46136</v>
       </c>
       <c r="B2" t="s">
-        <v>22</v>
+        <v>126</v>
       </c>
       <c r="C2" t="s">
-        <v>36</v>
+        <v>96</v>
       </c>
       <c r="D2">
         <f>VLOOKUP(B2,Teams!A:B,2,FALSE)</f>
@@ -953,18 +929,18 @@
         <v>1</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" s="2">
-        <v>46133</v>
+        <v>46136</v>
       </c>
       <c r="B3" t="s">
-        <v>41</v>
+        <v>71</v>
       </c>
       <c r="C3" t="s">
-        <v>103</v>
+        <v>85</v>
       </c>
       <c r="D3">
         <f>VLOOKUP(B3,Teams!A:B,2,FALSE)</f>
@@ -975,529 +951,130 @@
         <v>2</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="2">
-        <v>46133</v>
-      </c>
-      <c r="B4" t="s">
-        <v>71</v>
-      </c>
-      <c r="C4" t="s">
-        <v>66</v>
-      </c>
-      <c r="D4">
-        <f>VLOOKUP(B4,Teams!A:B,2,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="E4">
-        <f>VLOOKUP(C4,Teams!A:B,2,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="2">
-        <v>46133</v>
-      </c>
-      <c r="B5" t="s">
-        <v>95</v>
-      </c>
-      <c r="C5" t="s">
-        <v>48</v>
-      </c>
-      <c r="D5">
-        <f>VLOOKUP(B5,Teams!A:B,2,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="E5">
-        <f>VLOOKUP(C5,Teams!A:B,2,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="2">
-        <v>46133</v>
-      </c>
-      <c r="B6" t="s">
-        <v>99</v>
-      </c>
-      <c r="C6" t="s">
-        <v>143</v>
-      </c>
-      <c r="D6">
-        <f>VLOOKUP(B6,Teams!A:B,2,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="E6">
-        <f>VLOOKUP(C6,Teams!A:B,2,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="2">
-        <v>46133</v>
-      </c>
-      <c r="B7" t="s">
-        <v>105</v>
-      </c>
-      <c r="C7" t="s">
-        <v>128</v>
-      </c>
-      <c r="D7">
-        <f>VLOOKUP(B7,Teams!A:B,2,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="E7">
-        <f>VLOOKUP(C7,Teams!A:B,2,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="2">
-        <v>46133</v>
-      </c>
-      <c r="B8" t="s">
-        <v>119</v>
-      </c>
-      <c r="C8" t="s">
-        <v>23</v>
-      </c>
-      <c r="D8">
-        <f>VLOOKUP(B8,Teams!A:B,2,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="E8">
-        <f>VLOOKUP(C8,Teams!A:B,2,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="2">
-        <v>46133</v>
-      </c>
-      <c r="B9" t="s">
-        <v>125</v>
-      </c>
-      <c r="C9" t="s">
-        <v>85</v>
-      </c>
-      <c r="D9">
-        <f>VLOOKUP(B9,Teams!A:B,2,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="E9">
-        <f>VLOOKUP(C9,Teams!A:B,2,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="2">
-        <v>46133</v>
-      </c>
-      <c r="B10" t="s">
-        <v>136</v>
-      </c>
-      <c r="C10" t="s">
-        <v>135</v>
-      </c>
-      <c r="D10">
-        <f>VLOOKUP(B10,Teams!A:B,2,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="E10">
-        <f>VLOOKUP(C10,Teams!A:B,2,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="F10" s="3" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="2">
-        <v>46133</v>
-      </c>
-      <c r="B11" t="s">
-        <v>19</v>
-      </c>
-      <c r="C11" t="s">
-        <v>101</v>
-      </c>
-      <c r="D11">
-        <f>VLOOKUP(B11,Teams!A:B,2,FALSE)</f>
-        <v>3</v>
-      </c>
-      <c r="E11">
-        <f>VLOOKUP(C11,Teams!A:B,2,FALSE)</f>
-        <v>3</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="2">
-        <v>46133</v>
-      </c>
-      <c r="B12" t="s">
-        <v>49</v>
-      </c>
-      <c r="C12" t="s">
-        <v>73</v>
-      </c>
-      <c r="D12">
-        <f>VLOOKUP(B12,Teams!A:B,2,FALSE)</f>
-        <v>3</v>
-      </c>
-      <c r="E12">
-        <f>VLOOKUP(C12,Teams!A:B,2,FALSE)</f>
-        <v>3</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="2">
-        <v>46133</v>
-      </c>
-      <c r="B13" t="s">
-        <v>110</v>
-      </c>
-      <c r="C13" t="s">
-        <v>76</v>
-      </c>
-      <c r="D13">
-        <f>VLOOKUP(B13,Teams!A:B,2,FALSE)</f>
-        <v>3</v>
-      </c>
-      <c r="E13">
-        <f>VLOOKUP(C13,Teams!A:B,2,FALSE)</f>
-        <v>3</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="2">
-        <v>46133</v>
-      </c>
-      <c r="B14" t="s">
-        <v>123</v>
-      </c>
-      <c r="C14" t="s">
-        <v>11</v>
-      </c>
-      <c r="D14">
-        <f>VLOOKUP(B14,Teams!A:B,2,FALSE)</f>
-        <v>3</v>
-      </c>
-      <c r="E14">
-        <f>VLOOKUP(C14,Teams!A:B,2,FALSE)</f>
-        <v>3</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="2">
-        <v>46133</v>
-      </c>
-      <c r="B15" t="s">
-        <v>124</v>
-      </c>
-      <c r="C15" t="s">
-        <v>81</v>
-      </c>
-      <c r="D15">
-        <f>VLOOKUP(B15,Teams!A:B,2,FALSE)</f>
-        <v>3</v>
-      </c>
-      <c r="E15">
-        <f>VLOOKUP(C15,Teams!A:B,2,FALSE)</f>
-        <v>3</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="2">
-        <v>46133</v>
-      </c>
-      <c r="B16" t="s">
-        <v>32</v>
-      </c>
-      <c r="C16" t="s">
-        <v>60</v>
-      </c>
-      <c r="D16">
-        <f>VLOOKUP(B16,Teams!A:B,2,FALSE)</f>
-        <v>4</v>
-      </c>
-      <c r="E16">
-        <f>VLOOKUP(C16,Teams!A:B,2,FALSE)</f>
-        <v>4</v>
-      </c>
-      <c r="F16" s="3" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="2">
-        <v>46133</v>
-      </c>
-      <c r="B17" t="s">
-        <v>37</v>
-      </c>
-      <c r="C17" t="s">
-        <v>133</v>
-      </c>
-      <c r="D17">
-        <f>VLOOKUP(B17,Teams!A:B,2,FALSE)</f>
-        <v>4</v>
-      </c>
-      <c r="E17">
-        <f>VLOOKUP(C17,Teams!A:B,2,FALSE)</f>
-        <v>4</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="2">
-        <v>46134</v>
-      </c>
-      <c r="B18" t="s">
-        <v>0</v>
-      </c>
-      <c r="C18" t="s">
-        <v>70</v>
-      </c>
-      <c r="D18">
-        <f>VLOOKUP(B18,Teams!A:B,2,FALSE)</f>
-        <v>1</v>
-      </c>
-      <c r="E18">
-        <f>VLOOKUP(C18,Teams!A:B,2,FALSE)</f>
-        <v>1</v>
-      </c>
-      <c r="F18" s="3" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="2">
-        <v>46134</v>
-      </c>
-      <c r="B19" t="s">
-        <v>26</v>
-      </c>
-      <c r="C19" t="s">
-        <v>79</v>
-      </c>
-      <c r="D19">
-        <f>VLOOKUP(B19,Teams!A:B,2,FALSE)</f>
-        <v>1</v>
-      </c>
-      <c r="E19">
-        <f>VLOOKUP(C19,Teams!A:B,2,FALSE)</f>
-        <v>1</v>
-      </c>
-      <c r="F19" s="3" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="2">
-        <v>46134</v>
-      </c>
-      <c r="B20" t="s">
-        <v>13</v>
-      </c>
-      <c r="C20" t="s">
-        <v>104</v>
-      </c>
-      <c r="D20">
-        <f>VLOOKUP(B20,Teams!A:B,2,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="E20">
-        <f>VLOOKUP(C20,Teams!A:B,2,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="2">
-        <v>46134</v>
-      </c>
-      <c r="B21" t="s">
-        <v>35</v>
-      </c>
-      <c r="C21" t="s">
-        <v>67</v>
-      </c>
-      <c r="D21">
-        <f>VLOOKUP(B21,Teams!A:B,2,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="E21">
-        <f>VLOOKUP(C21,Teams!A:B,2,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="2">
-        <v>46134</v>
-      </c>
-      <c r="B22" t="s">
-        <v>83</v>
-      </c>
-      <c r="C22" t="s">
-        <v>116</v>
-      </c>
-      <c r="D22">
-        <f>VLOOKUP(B22,Teams!A:B,2,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="E22">
-        <f>VLOOKUP(C22,Teams!A:B,2,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="2">
-        <v>46134</v>
-      </c>
-      <c r="B23" t="s">
-        <v>115</v>
-      </c>
-      <c r="C23" t="s">
-        <v>14</v>
-      </c>
-      <c r="D23">
-        <f>VLOOKUP(B23,Teams!A:B,2,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="E23">
-        <f>VLOOKUP(C23,Teams!A:B,2,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="F23" s="3" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="2">
-        <v>46134</v>
-      </c>
-      <c r="B24" t="s">
-        <v>33</v>
-      </c>
-      <c r="C24" t="s">
-        <v>102</v>
-      </c>
-      <c r="D24">
-        <f>VLOOKUP(B24,Teams!A:B,2,FALSE)</f>
-        <v>3</v>
-      </c>
-      <c r="E24">
-        <f>VLOOKUP(C24,Teams!A:B,2,FALSE)</f>
-        <v>3</v>
-      </c>
-      <c r="F24" s="3" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A4" s="2"/>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A5" s="2"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A6" s="2"/>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A7" s="2"/>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A8" s="2"/>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A9" s="2"/>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A10" s="2"/>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A11" s="2"/>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A12" s="2"/>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A13" s="2"/>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A14" s="2"/>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A15" s="2"/>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A16" s="2"/>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A17" s="2"/>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A18" s="2"/>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A19" s="2"/>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A20" s="2"/>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A21" s="2"/>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A22" s="2"/>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A23" s="2"/>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A24" s="2"/>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A25" s="2"/>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A26" s="2"/>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A27" s="2"/>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A28" s="2"/>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A29" s="2"/>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A30" s="2"/>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A31" s="2"/>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A32" s="2"/>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A33" s="2"/>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A34" s="2"/>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A35" s="2"/>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A36" s="2"/>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A37" s="2"/>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A38" s="2"/>
     </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A39" s="2"/>
     </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A40" s="2"/>
     </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A41" s="2"/>
     </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A42" s="2"/>
     </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A43" s="2"/>
     </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A44" s="2"/>
     </row>
   </sheetData>
@@ -1520,13 +1097,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{660D5CBD-EF61-4F28-8F5F-C3B953B1D14A}">
   <dimension ref="A1:B147"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="23" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.7109375" style="1"/>
+    <col min="2" max="2" width="8.7265625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1534,7 +1111,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -1542,7 +1119,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -1550,7 +1127,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1558,7 +1135,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -1566,7 +1143,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -1574,7 +1151,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -1582,7 +1159,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -1590,7 +1167,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>8</v>
       </c>
@@ -1598,7 +1175,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>9</v>
       </c>
@@ -1606,7 +1183,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>10</v>
       </c>
@@ -1614,7 +1191,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>11</v>
       </c>
@@ -1622,7 +1199,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>12</v>
       </c>
@@ -1630,7 +1207,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>13</v>
       </c>
@@ -1638,7 +1215,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>14</v>
       </c>
@@ -1646,7 +1223,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>15</v>
       </c>
@@ -1654,7 +1231,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>16</v>
       </c>
@@ -1662,7 +1239,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>17</v>
       </c>
@@ -1670,7 +1247,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>18</v>
       </c>
@@ -1678,7 +1255,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>19</v>
       </c>
@@ -1686,7 +1263,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>20</v>
       </c>
@@ -1694,7 +1271,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>21</v>
       </c>
@@ -1702,7 +1279,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>22</v>
       </c>
@@ -1710,7 +1287,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>23</v>
       </c>
@@ -1718,7 +1295,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>24</v>
       </c>
@@ -1726,7 +1303,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>25</v>
       </c>
@@ -1734,7 +1311,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>26</v>
       </c>
@@ -1742,7 +1319,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>27</v>
       </c>
@@ -1750,7 +1327,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>28</v>
       </c>
@@ -1758,7 +1335,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>29</v>
       </c>
@@ -1766,7 +1343,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>30</v>
       </c>
@@ -1774,7 +1351,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>31</v>
       </c>
@@ -1782,7 +1359,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>32</v>
       </c>
@@ -1790,7 +1367,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>33</v>
       </c>
@@ -1798,7 +1375,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>34</v>
       </c>
@@ -1806,7 +1383,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>35</v>
       </c>
@@ -1814,7 +1391,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>36</v>
       </c>
@@ -1822,7 +1399,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>37</v>
       </c>
@@ -1830,7 +1407,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>38</v>
       </c>
@@ -1838,7 +1415,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>39</v>
       </c>
@@ -1846,7 +1423,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>40</v>
       </c>
@@ -1854,7 +1431,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>41</v>
       </c>
@@ -1862,7 +1439,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>42</v>
       </c>
@@ -1870,7 +1447,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>43</v>
       </c>
@@ -1878,7 +1455,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>44</v>
       </c>
@@ -1886,7 +1463,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>45</v>
       </c>
@@ -1894,7 +1471,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>46</v>
       </c>
@@ -1902,7 +1479,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>47</v>
       </c>
@@ -1910,7 +1487,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>48</v>
       </c>
@@ -1918,7 +1495,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>49</v>
       </c>
@@ -1926,7 +1503,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>50</v>
       </c>
@@ -1934,7 +1511,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>51</v>
       </c>
@@ -1942,7 +1519,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>52</v>
       </c>
@@ -1950,7 +1527,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>53</v>
       </c>
@@ -1958,7 +1535,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>54</v>
       </c>
@@ -1966,7 +1543,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>55</v>
       </c>
@@ -1974,7 +1551,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>56</v>
       </c>
@@ -1982,7 +1559,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>57</v>
       </c>
@@ -1990,7 +1567,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>58</v>
       </c>
@@ -1998,7 +1575,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>59</v>
       </c>
@@ -2006,7 +1583,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>60</v>
       </c>
@@ -2014,7 +1591,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>61</v>
       </c>
@@ -2022,7 +1599,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>62</v>
       </c>
@@ -2030,7 +1607,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>63</v>
       </c>
@@ -2038,7 +1615,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>64</v>
       </c>
@@ -2046,7 +1623,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>65</v>
       </c>
@@ -2054,7 +1631,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>66</v>
       </c>
@@ -2062,7 +1639,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>67</v>
       </c>
@@ -2070,7 +1647,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>68</v>
       </c>
@@ -2078,7 +1655,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>69</v>
       </c>
@@ -2086,7 +1663,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>70</v>
       </c>
@@ -2094,7 +1671,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>71</v>
       </c>
@@ -2102,7 +1679,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>72</v>
       </c>
@@ -2110,7 +1687,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>73</v>
       </c>
@@ -2118,7 +1695,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>74</v>
       </c>
@@ -2126,7 +1703,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>75</v>
       </c>
@@ -2134,7 +1711,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>76</v>
       </c>
@@ -2142,7 +1719,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
         <v>77</v>
       </c>
@@ -2150,7 +1727,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
         <v>78</v>
       </c>
@@ -2158,7 +1735,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
         <v>79</v>
       </c>
@@ -2166,7 +1743,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>80</v>
       </c>
@@ -2174,7 +1751,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
         <v>81</v>
       </c>
@@ -2182,7 +1759,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
         <v>82</v>
       </c>
@@ -2190,7 +1767,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
         <v>83</v>
       </c>
@@ -2198,7 +1775,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
         <v>84</v>
       </c>
@@ -2206,7 +1783,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
         <v>85</v>
       </c>
@@ -2214,7 +1791,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
         <v>86</v>
       </c>
@@ -2222,7 +1799,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
         <v>87</v>
       </c>
@@ -2230,7 +1807,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
         <v>88</v>
       </c>
@@ -2238,7 +1815,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
         <v>89</v>
       </c>
@@ -2246,7 +1823,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
         <v>90</v>
       </c>
@@ -2254,7 +1831,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
         <v>91</v>
       </c>
@@ -2262,7 +1839,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
         <v>92</v>
       </c>
@@ -2270,7 +1847,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
         <v>93</v>
       </c>
@@ -2278,7 +1855,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
         <v>94</v>
       </c>
@@ -2286,7 +1863,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
         <v>95</v>
       </c>
@@ -2294,7 +1871,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
         <v>96</v>
       </c>
@@ -2302,7 +1879,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
         <v>97</v>
       </c>
@@ -2310,7 +1887,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
         <v>98</v>
       </c>
@@ -2318,7 +1895,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
         <v>99</v>
       </c>
@@ -2326,7 +1903,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
         <v>100</v>
       </c>
@@ -2334,7 +1911,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="102" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
         <v>101</v>
       </c>
@@ -2342,7 +1919,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="103" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
         <v>102</v>
       </c>
@@ -2350,7 +1927,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="104" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
         <v>103</v>
       </c>
@@ -2358,7 +1935,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="105" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
         <v>104</v>
       </c>
@@ -2366,7 +1943,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="106" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
         <v>105</v>
       </c>
@@ -2374,7 +1951,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="107" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
         <v>106</v>
       </c>
@@ -2382,7 +1959,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="108" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
         <v>107</v>
       </c>
@@ -2390,7 +1967,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="109" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
         <v>108</v>
       </c>
@@ -2398,7 +1975,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="110" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
         <v>109</v>
       </c>
@@ -2406,7 +1983,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="111" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
         <v>110</v>
       </c>
@@ -2414,7 +1991,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="112" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
         <v>111</v>
       </c>
@@ -2422,7 +1999,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="113" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
         <v>112</v>
       </c>
@@ -2430,7 +2007,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="114" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
         <v>113</v>
       </c>
@@ -2438,7 +2015,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="115" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
         <v>114</v>
       </c>
@@ -2446,7 +2023,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="116" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
         <v>115</v>
       </c>
@@ -2454,7 +2031,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="117" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
         <v>116</v>
       </c>
@@ -2462,7 +2039,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="118" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
         <v>117</v>
       </c>
@@ -2470,7 +2047,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="119" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
         <v>118</v>
       </c>
@@ -2478,7 +2055,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="120" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
         <v>119</v>
       </c>
@@ -2486,7 +2063,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="121" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
         <v>120</v>
       </c>
@@ -2494,7 +2071,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="122" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
         <v>121</v>
       </c>
@@ -2502,7 +2079,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="123" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
         <v>122</v>
       </c>
@@ -2510,7 +2087,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="124" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
         <v>123</v>
       </c>
@@ -2518,7 +2095,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="125" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
         <v>124</v>
       </c>
@@ -2526,7 +2103,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="126" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
         <v>125</v>
       </c>
@@ -2534,7 +2111,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="127" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
         <v>126</v>
       </c>
@@ -2542,7 +2119,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="128" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
         <v>127</v>
       </c>
@@ -2550,7 +2127,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="129" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
         <v>128</v>
       </c>
@@ -2558,7 +2135,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="130" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
         <v>129</v>
       </c>
@@ -2566,7 +2143,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="131" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
         <v>130</v>
       </c>
@@ -2574,7 +2151,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="132" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
         <v>131</v>
       </c>
@@ -2582,7 +2159,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="133" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
         <v>132</v>
       </c>
@@ -2590,7 +2167,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="134" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
         <v>133</v>
       </c>
@@ -2598,7 +2175,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="135" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
         <v>134</v>
       </c>
@@ -2606,7 +2183,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="136" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
         <v>135</v>
       </c>
@@ -2614,7 +2191,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="137" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
         <v>136</v>
       </c>
@@ -2622,7 +2199,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="138" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
         <v>137</v>
       </c>
@@ -2630,7 +2207,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="139" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
         <v>138</v>
       </c>
@@ -2638,7 +2215,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="140" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
         <v>139</v>
       </c>
@@ -2646,7 +2223,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="141" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
         <v>140</v>
       </c>
@@ -2654,7 +2231,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="142" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
         <v>141</v>
       </c>
@@ -2662,7 +2239,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="143" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
         <v>142</v>
       </c>
@@ -2670,7 +2247,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="144" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
         <v>143</v>
       </c>
@@ -2678,7 +2255,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="145" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A145" t="s">
         <v>144</v>
       </c>
@@ -2686,7 +2263,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="146" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
         <v>145</v>
       </c>
@@ -2694,7 +2271,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="147" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A147" t="s">
         <v>146</v>
       </c>

--- a/.github/tmp_results.xlsx
+++ b/.github/tmp_results.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sean Elvidge\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A214FFC0-653A-4591-A828-CBC67DA4E04B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8538E2C-E36B-4923-AE45-5650C52DE17B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20" yWindow="740" windowWidth="19180" windowHeight="11260" xr2:uid="{156B8CF3-2535-45A6-80D2-358CC30668D6}"/>
+    <workbookView xWindow="20" yWindow="20" windowWidth="19180" windowHeight="11260" xr2:uid="{156B8CF3-2535-45A6-80D2-358CC30668D6}"/>
   </bookViews>
   <sheets>
     <sheet name="Scores" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="174">
   <si>
     <t>AFC Bournemouth</t>
   </si>
@@ -504,7 +504,61 @@
     <t>1-1</t>
   </si>
   <si>
-    <t>0-5</t>
+    <t>1-0</t>
+  </si>
+  <si>
+    <t>3-1</t>
+  </si>
+  <si>
+    <t>2-1</t>
+  </si>
+  <si>
+    <t>0-1</t>
+  </si>
+  <si>
+    <t>5-1</t>
+  </si>
+  <si>
+    <t>0-0</t>
+  </si>
+  <si>
+    <t>4-1</t>
+  </si>
+  <si>
+    <t>2-3</t>
+  </si>
+  <si>
+    <t>1-3</t>
+  </si>
+  <si>
+    <t>1-4</t>
+  </si>
+  <si>
+    <t>4-3</t>
+  </si>
+  <si>
+    <t>4-0</t>
+  </si>
+  <si>
+    <t>3-0</t>
+  </si>
+  <si>
+    <t>3-3</t>
+  </si>
+  <si>
+    <t>6-2</t>
+  </si>
+  <si>
+    <t>2-0</t>
+  </si>
+  <si>
+    <t>3-2</t>
+  </si>
+  <si>
+    <t>2-2</t>
+  </si>
+  <si>
+    <t>0-2</t>
   </si>
 </sst>
 </file>
@@ -912,13 +966,13 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" s="2">
-        <v>46136</v>
+        <v>46137</v>
       </c>
       <c r="B2" t="s">
-        <v>126</v>
+        <v>55</v>
       </c>
       <c r="C2" t="s">
-        <v>96</v>
+        <v>9</v>
       </c>
       <c r="D2">
         <f>VLOOKUP(B2,Teams!A:B,2,FALSE)</f>
@@ -934,147 +988,812 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" s="2">
-        <v>46136</v>
+        <v>46137</v>
       </c>
       <c r="B3" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C3" t="s">
-        <v>85</v>
+        <v>44</v>
       </c>
       <c r="D3">
         <f>VLOOKUP(B3,Teams!A:B,2,FALSE)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E3">
         <f>VLOOKUP(C3,Teams!A:B,2,FALSE)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F3" s="3" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A4" s="2">
+        <v>46137</v>
+      </c>
+      <c r="B4" t="s">
+        <v>137</v>
+      </c>
+      <c r="C4" t="s">
+        <v>51</v>
+      </c>
+      <c r="D4">
+        <f>VLOOKUP(B4,Teams!A:B,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="E4">
+        <f>VLOOKUP(C4,Teams!A:B,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A5" s="2">
+        <v>46137</v>
+      </c>
+      <c r="B5" t="s">
+        <v>141</v>
+      </c>
+      <c r="C5" t="s">
+        <v>132</v>
+      </c>
+      <c r="D5">
+        <f>VLOOKUP(B5,Teams!A:B,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="E5">
+        <f>VLOOKUP(C5,Teams!A:B,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A6" s="2">
+        <v>46137</v>
+      </c>
+      <c r="B6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" t="s">
+        <v>91</v>
+      </c>
+      <c r="D6">
+        <f>VLOOKUP(B6,Teams!A:B,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="E6">
+        <f>VLOOKUP(C6,Teams!A:B,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A7" s="2">
+        <v>46137</v>
+      </c>
+      <c r="B7" t="s">
+        <v>35</v>
+      </c>
+      <c r="C7" t="s">
+        <v>66</v>
+      </c>
+      <c r="D7">
+        <f>VLOOKUP(B7,Teams!A:B,2,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="E7">
+        <f>VLOOKUP(C7,Teams!A:B,2,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A8" s="2">
+        <v>46137</v>
+      </c>
+      <c r="B8" t="s">
+        <v>83</v>
+      </c>
+      <c r="C8" t="s">
+        <v>135</v>
+      </c>
+      <c r="D8">
+        <f>VLOOKUP(B8,Teams!A:B,2,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="E8">
+        <f>VLOOKUP(C8,Teams!A:B,2,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A9" s="2">
+        <v>46137</v>
+      </c>
+      <c r="B9" t="s">
+        <v>136</v>
+      </c>
+      <c r="C9" t="s">
+        <v>67</v>
+      </c>
+      <c r="D9">
+        <f>VLOOKUP(B9,Teams!A:B,2,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="E9">
+        <f>VLOOKUP(C9,Teams!A:B,2,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A10" s="2">
+        <v>46137</v>
+      </c>
+      <c r="B10" t="s">
+        <v>13</v>
+      </c>
+      <c r="C10" t="s">
+        <v>23</v>
+      </c>
+      <c r="D10">
+        <f>VLOOKUP(B10,Teams!A:B,2,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="E10">
+        <f>VLOOKUP(C10,Teams!A:B,2,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A11" s="2">
+        <v>46137</v>
+      </c>
+      <c r="B11" t="s">
+        <v>95</v>
+      </c>
+      <c r="C11" t="s">
+        <v>128</v>
+      </c>
+      <c r="D11">
+        <f>VLOOKUP(B11,Teams!A:B,2,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="E11">
+        <f>VLOOKUP(C11,Teams!A:B,2,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="F11" s="3" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A4" s="2"/>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A5" s="2"/>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A6" s="2"/>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A7" s="2"/>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A8" s="2"/>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A9" s="2"/>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A10" s="2"/>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A11" s="2"/>
-    </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A12" s="2"/>
+      <c r="A12" s="2">
+        <v>46137</v>
+      </c>
+      <c r="B12" t="s">
+        <v>99</v>
+      </c>
+      <c r="C12" t="s">
+        <v>116</v>
+      </c>
+      <c r="D12">
+        <f>VLOOKUP(B12,Teams!A:B,2,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="E12">
+        <f>VLOOKUP(C12,Teams!A:B,2,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>161</v>
+      </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A13" s="2"/>
+      <c r="A13" s="2">
+        <v>46137</v>
+      </c>
+      <c r="B13" t="s">
+        <v>105</v>
+      </c>
+      <c r="C13" t="s">
+        <v>48</v>
+      </c>
+      <c r="D13">
+        <f>VLOOKUP(B13,Teams!A:B,2,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="E13">
+        <f>VLOOKUP(C13,Teams!A:B,2,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>162</v>
+      </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A14" s="2"/>
+      <c r="A14" s="2">
+        <v>46137</v>
+      </c>
+      <c r="B14" t="s">
+        <v>115</v>
+      </c>
+      <c r="C14" t="s">
+        <v>104</v>
+      </c>
+      <c r="D14">
+        <f>VLOOKUP(B14,Teams!A:B,2,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="E14">
+        <f>VLOOKUP(C14,Teams!A:B,2,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>162</v>
+      </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A15" s="2"/>
+      <c r="A15" s="2">
+        <v>46137</v>
+      </c>
+      <c r="B15" t="s">
+        <v>125</v>
+      </c>
+      <c r="C15" t="s">
+        <v>103</v>
+      </c>
+      <c r="D15">
+        <f>VLOOKUP(B15,Teams!A:B,2,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="E15">
+        <f>VLOOKUP(C15,Teams!A:B,2,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>163</v>
+      </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A16" s="2"/>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A17" s="2"/>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A18" s="2"/>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A19" s="2"/>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A20" s="2"/>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A21" s="2"/>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A22" s="2"/>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A23" s="2"/>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A24" s="2"/>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A25" s="2"/>
-    </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A26" s="2"/>
-    </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A27" s="2"/>
-    </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A28" s="2"/>
-    </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A29" s="2"/>
-    </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A30" s="2"/>
-    </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A31" s="2"/>
-    </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A32" s="2"/>
-    </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A33" s="2"/>
-    </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A34" s="2"/>
-    </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A35" s="2"/>
-    </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A36" s="2"/>
-    </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A37" s="2"/>
-    </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A38" s="2"/>
-    </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A16" s="2">
+        <v>46137</v>
+      </c>
+      <c r="B16" t="s">
+        <v>49</v>
+      </c>
+      <c r="C16" t="s">
+        <v>123</v>
+      </c>
+      <c r="D16">
+        <f>VLOOKUP(B16,Teams!A:B,2,FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="E16">
+        <f>VLOOKUP(C16,Teams!A:B,2,FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A17" s="2">
+        <v>46137</v>
+      </c>
+      <c r="B17" t="s">
+        <v>124</v>
+      </c>
+      <c r="C17" t="s">
+        <v>100</v>
+      </c>
+      <c r="D17">
+        <f>VLOOKUP(B17,Teams!A:B,2,FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="E17">
+        <f>VLOOKUP(C17,Teams!A:B,2,FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A18" s="2">
+        <v>46137</v>
+      </c>
+      <c r="B18" t="s">
+        <v>15</v>
+      </c>
+      <c r="C18" t="s">
+        <v>72</v>
+      </c>
+      <c r="D18">
+        <f>VLOOKUP(B18,Teams!A:B,2,FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="E18">
+        <f>VLOOKUP(C18,Teams!A:B,2,FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A19" s="2">
+        <v>46137</v>
+      </c>
+      <c r="B19" t="s">
+        <v>19</v>
+      </c>
+      <c r="C19" t="s">
+        <v>16</v>
+      </c>
+      <c r="D19">
+        <f>VLOOKUP(B19,Teams!A:B,2,FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="E19">
+        <f>VLOOKUP(C19,Teams!A:B,2,FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A20" s="2">
+        <v>46137</v>
+      </c>
+      <c r="B20" t="s">
+        <v>27</v>
+      </c>
+      <c r="C20" t="s">
+        <v>52</v>
+      </c>
+      <c r="D20">
+        <f>VLOOKUP(B20,Teams!A:B,2,FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="E20">
+        <f>VLOOKUP(C20,Teams!A:B,2,FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A21" s="2">
+        <v>46137</v>
+      </c>
+      <c r="B21" t="s">
+        <v>33</v>
+      </c>
+      <c r="C21" t="s">
+        <v>93</v>
+      </c>
+      <c r="D21">
+        <f>VLOOKUP(B21,Teams!A:B,2,FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="E21">
+        <f>VLOOKUP(C21,Teams!A:B,2,FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A22" s="2">
+        <v>46137</v>
+      </c>
+      <c r="B22" t="s">
+        <v>65</v>
+      </c>
+      <c r="C22" t="s">
+        <v>81</v>
+      </c>
+      <c r="D22">
+        <f>VLOOKUP(B22,Teams!A:B,2,FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="E22">
+        <f>VLOOKUP(C22,Teams!A:B,2,FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A23" s="2">
+        <v>46137</v>
+      </c>
+      <c r="B23" t="s">
+        <v>73</v>
+      </c>
+      <c r="C23" t="s">
+        <v>144</v>
+      </c>
+      <c r="D23">
+        <f>VLOOKUP(B23,Teams!A:B,2,FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="E23">
+        <f>VLOOKUP(C23,Teams!A:B,2,FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A24" s="2">
+        <v>46137</v>
+      </c>
+      <c r="B24" t="s">
+        <v>76</v>
+      </c>
+      <c r="C24" t="s">
+        <v>11</v>
+      </c>
+      <c r="D24">
+        <f>VLOOKUP(B24,Teams!A:B,2,FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="E24">
+        <f>VLOOKUP(C24,Teams!A:B,2,FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A25" s="2">
+        <v>46137</v>
+      </c>
+      <c r="B25" t="s">
+        <v>101</v>
+      </c>
+      <c r="C25" t="s">
+        <v>102</v>
+      </c>
+      <c r="D25">
+        <f>VLOOKUP(B25,Teams!A:B,2,FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="E25">
+        <f>VLOOKUP(C25,Teams!A:B,2,FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A26" s="2">
+        <v>46137</v>
+      </c>
+      <c r="B26" t="s">
+        <v>110</v>
+      </c>
+      <c r="C26" t="s">
+        <v>106</v>
+      </c>
+      <c r="D26">
+        <f>VLOOKUP(B26,Teams!A:B,2,FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="E26">
+        <f>VLOOKUP(C26,Teams!A:B,2,FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A27" s="2">
+        <v>46137</v>
+      </c>
+      <c r="B27" t="s">
+        <v>138</v>
+      </c>
+      <c r="C27" t="s">
+        <v>1</v>
+      </c>
+      <c r="D27">
+        <f>VLOOKUP(B27,Teams!A:B,2,FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="E27">
+        <f>VLOOKUP(C27,Teams!A:B,2,FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A28" s="2">
+        <v>46137</v>
+      </c>
+      <c r="B28" t="s">
+        <v>60</v>
+      </c>
+      <c r="C28" t="s">
+        <v>129</v>
+      </c>
+      <c r="D28">
+        <f>VLOOKUP(B28,Teams!A:B,2,FALSE)</f>
+        <v>4</v>
+      </c>
+      <c r="E28">
+        <f>VLOOKUP(C28,Teams!A:B,2,FALSE)</f>
+        <v>4</v>
+      </c>
+      <c r="F28" s="3" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A29" s="2">
+        <v>46137</v>
+      </c>
+      <c r="B29" t="s">
+        <v>86</v>
+      </c>
+      <c r="C29" t="s">
+        <v>133</v>
+      </c>
+      <c r="D29">
+        <f>VLOOKUP(B29,Teams!A:B,2,FALSE)</f>
+        <v>4</v>
+      </c>
+      <c r="E29">
+        <f>VLOOKUP(C29,Teams!A:B,2,FALSE)</f>
+        <v>4</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A30" s="2">
+        <v>46137</v>
+      </c>
+      <c r="B30" t="s">
+        <v>4</v>
+      </c>
+      <c r="C30" t="s">
+        <v>42</v>
+      </c>
+      <c r="D30">
+        <f>VLOOKUP(B30,Teams!A:B,2,FALSE)</f>
+        <v>4</v>
+      </c>
+      <c r="E30">
+        <f>VLOOKUP(C30,Teams!A:B,2,FALSE)</f>
+        <v>4</v>
+      </c>
+      <c r="F30" s="3" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A31" s="2">
+        <v>46137</v>
+      </c>
+      <c r="B31" t="s">
+        <v>10</v>
+      </c>
+      <c r="C31" t="s">
+        <v>58</v>
+      </c>
+      <c r="D31">
+        <f>VLOOKUP(B31,Teams!A:B,2,FALSE)</f>
+        <v>4</v>
+      </c>
+      <c r="E31">
+        <f>VLOOKUP(C31,Teams!A:B,2,FALSE)</f>
+        <v>4</v>
+      </c>
+      <c r="F31" s="3" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A32" s="2">
+        <v>46137</v>
+      </c>
+      <c r="B32" t="s">
+        <v>24</v>
+      </c>
+      <c r="C32" t="s">
+        <v>37</v>
+      </c>
+      <c r="D32">
+        <f>VLOOKUP(B32,Teams!A:B,2,FALSE)</f>
+        <v>4</v>
+      </c>
+      <c r="E32">
+        <f>VLOOKUP(C32,Teams!A:B,2,FALSE)</f>
+        <v>4</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A33" s="2">
+        <v>46137</v>
+      </c>
+      <c r="B33" t="s">
+        <v>32</v>
+      </c>
+      <c r="C33" t="s">
+        <v>12</v>
+      </c>
+      <c r="D33">
+        <f>VLOOKUP(B33,Teams!A:B,2,FALSE)</f>
+        <v>4</v>
+      </c>
+      <c r="E33">
+        <f>VLOOKUP(C33,Teams!A:B,2,FALSE)</f>
+        <v>4</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A34" s="2">
+        <v>46137</v>
+      </c>
+      <c r="B34" t="s">
+        <v>39</v>
+      </c>
+      <c r="C34" t="s">
+        <v>43</v>
+      </c>
+      <c r="D34">
+        <f>VLOOKUP(B34,Teams!A:B,2,FALSE)</f>
+        <v>4</v>
+      </c>
+      <c r="E34">
+        <f>VLOOKUP(C34,Teams!A:B,2,FALSE)</f>
+        <v>4</v>
+      </c>
+      <c r="F34" s="3" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A35" s="2">
+        <v>46137</v>
+      </c>
+      <c r="B35" t="s">
+        <v>40</v>
+      </c>
+      <c r="C35" t="s">
+        <v>97</v>
+      </c>
+      <c r="D35">
+        <f>VLOOKUP(B35,Teams!A:B,2,FALSE)</f>
+        <v>4</v>
+      </c>
+      <c r="E35">
+        <f>VLOOKUP(C35,Teams!A:B,2,FALSE)</f>
+        <v>4</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A36" s="2">
+        <v>46137</v>
+      </c>
+      <c r="B36" t="s">
+        <v>92</v>
+      </c>
+      <c r="C36" t="s">
+        <v>98</v>
+      </c>
+      <c r="D36">
+        <f>VLOOKUP(B36,Teams!A:B,2,FALSE)</f>
+        <v>4</v>
+      </c>
+      <c r="E36">
+        <f>VLOOKUP(C36,Teams!A:B,2,FALSE)</f>
+        <v>4</v>
+      </c>
+      <c r="F36" s="3" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A37" s="2">
+        <v>46137</v>
+      </c>
+      <c r="B37" t="s">
+        <v>117</v>
+      </c>
+      <c r="C37" t="s">
+        <v>53</v>
+      </c>
+      <c r="D37">
+        <f>VLOOKUP(B37,Teams!A:B,2,FALSE)</f>
+        <v>4</v>
+      </c>
+      <c r="E37">
+        <f>VLOOKUP(C37,Teams!A:B,2,FALSE)</f>
+        <v>4</v>
+      </c>
+      <c r="F37" s="3" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A38" s="2">
+        <v>46137</v>
+      </c>
+      <c r="B38" t="s">
+        <v>134</v>
+      </c>
+      <c r="C38" t="s">
+        <v>62</v>
+      </c>
+      <c r="D38">
+        <f>VLOOKUP(B38,Teams!A:B,2,FALSE)</f>
+        <v>4</v>
+      </c>
+      <c r="E38">
+        <f>VLOOKUP(C38,Teams!A:B,2,FALSE)</f>
+        <v>4</v>
+      </c>
+      <c r="F38" s="3" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A39" s="2"/>
     </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A40" s="2"/>
     </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A41" s="2"/>
     </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A42" s="2"/>
     </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A43" s="2"/>
     </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A44" s="2"/>
     </row>
   </sheetData>

--- a/.github/tmp_results.xlsx
+++ b/.github/tmp_results.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sean Elvidge\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8538E2C-E36B-4923-AE45-5650C52DE17B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E84A7ABC-8BE1-4D50-9F4A-EF9BFF7CDA0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20" yWindow="20" windowWidth="19180" windowHeight="11260" xr2:uid="{156B8CF3-2535-45A6-80D2-358CC30668D6}"/>
+    <workbookView xWindow="25695" yWindow="0" windowWidth="26010" windowHeight="20985" xr2:uid="{156B8CF3-2535-45A6-80D2-358CC30668D6}"/>
   </bookViews>
   <sheets>
     <sheet name="Scores" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="172">
   <si>
     <t>AFC Bournemouth</t>
   </si>
@@ -516,15 +516,9 @@
     <t>0-1</t>
   </si>
   <si>
-    <t>5-1</t>
-  </si>
-  <si>
     <t>0-0</t>
   </si>
   <si>
-    <t>4-1</t>
-  </si>
-  <si>
     <t>2-3</t>
   </si>
   <si>
@@ -534,9 +528,6 @@
     <t>1-4</t>
   </si>
   <si>
-    <t>4-3</t>
-  </si>
-  <si>
     <t>4-0</t>
   </si>
   <si>
@@ -546,9 +537,6 @@
     <t>3-3</t>
   </si>
   <si>
-    <t>6-2</t>
-  </si>
-  <si>
     <t>2-0</t>
   </si>
   <si>
@@ -558,7 +546,13 @@
     <t>2-2</t>
   </si>
   <si>
-    <t>0-2</t>
+    <t>1-2</t>
+  </si>
+  <si>
+    <t>0-4</t>
+  </si>
+  <si>
+    <t>1-5</t>
   </si>
 </sst>
 </file>
@@ -935,16 +929,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{944D37C4-CAD2-4526-8947-361FF9BC37B9}">
-  <dimension ref="A1:F44"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:F45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.54296875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.81640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.85546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="23" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.7265625" style="3"/>
+    <col min="6" max="6" width="8.7109375" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>149</v>
       </c>
@@ -964,15 +958,15 @@
         <v>152</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
-        <v>46137</v>
+        <v>46270</v>
       </c>
       <c r="B2" t="s">
-        <v>55</v>
+        <v>91</v>
       </c>
       <c r="C2" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="D2">
         <f>VLOOKUP(B2,Teams!A:B,2,FALSE)</f>
@@ -983,18 +977,18 @@
         <v>1</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
-        <v>46137</v>
+        <v>46270</v>
       </c>
       <c r="B3" t="s">
-        <v>74</v>
+        <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>44</v>
+        <v>126</v>
       </c>
       <c r="D3">
         <f>VLOOKUP(B3,Teams!A:B,2,FALSE)</f>
@@ -1005,18 +999,18 @@
         <v>1</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
-        <v>46137</v>
+        <v>46270</v>
       </c>
       <c r="B4" t="s">
-        <v>137</v>
+        <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>51</v>
+        <v>70</v>
       </c>
       <c r="D4">
         <f>VLOOKUP(B4,Teams!A:B,2,FALSE)</f>
@@ -1027,18 +1021,18 @@
         <v>1</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
-        <v>46137</v>
+        <v>46270</v>
       </c>
       <c r="B5" t="s">
-        <v>141</v>
+        <v>55</v>
       </c>
       <c r="C5" t="s">
-        <v>132</v>
+        <v>44</v>
       </c>
       <c r="D5">
         <f>VLOOKUP(B5,Teams!A:B,2,FALSE)</f>
@@ -1049,18 +1043,18 @@
         <v>1</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
-        <v>46137</v>
+        <v>46270</v>
       </c>
       <c r="B6" t="s">
-        <v>7</v>
+        <v>79</v>
       </c>
       <c r="C6" t="s">
-        <v>91</v>
+        <v>41</v>
       </c>
       <c r="D6">
         <f>VLOOKUP(B6,Teams!A:B,2,FALSE)</f>
@@ -1074,59 +1068,59 @@
         <v>155</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
-        <v>46137</v>
+        <v>46270</v>
       </c>
       <c r="B7" t="s">
-        <v>35</v>
+        <v>96</v>
       </c>
       <c r="C7" t="s">
-        <v>66</v>
+        <v>132</v>
       </c>
       <c r="D7">
         <f>VLOOKUP(B7,Teams!A:B,2,FALSE)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E7">
         <f>VLOOKUP(C7,Teams!A:B,2,FALSE)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
-        <v>46137</v>
+        <v>46270</v>
       </c>
       <c r="B8" t="s">
-        <v>83</v>
+        <v>66</v>
       </c>
       <c r="C8" t="s">
-        <v>135</v>
+        <v>9</v>
       </c>
       <c r="D8">
         <f>VLOOKUP(B8,Teams!A:B,2,FALSE)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E8">
         <f>VLOOKUP(C8,Teams!A:B,2,FALSE)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F8" s="3" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
-        <v>46137</v>
+        <v>46270</v>
       </c>
       <c r="B9" t="s">
-        <v>136</v>
+        <v>73</v>
       </c>
       <c r="C9" t="s">
-        <v>67</v>
+        <v>119</v>
       </c>
       <c r="D9">
         <f>VLOOKUP(B9,Teams!A:B,2,FALSE)</f>
@@ -1137,18 +1131,18 @@
         <v>2</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
-        <v>46137</v>
+        <v>46270</v>
       </c>
       <c r="B10" t="s">
-        <v>13</v>
+        <v>104</v>
       </c>
       <c r="C10" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="D10">
         <f>VLOOKUP(B10,Teams!A:B,2,FALSE)</f>
@@ -1162,15 +1156,15 @@
         <v>157</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
-        <v>46137</v>
+        <v>46270</v>
       </c>
       <c r="B11" t="s">
-        <v>95</v>
+        <v>125</v>
       </c>
       <c r="C11" t="s">
-        <v>128</v>
+        <v>35</v>
       </c>
       <c r="D11">
         <f>VLOOKUP(B11,Teams!A:B,2,FALSE)</f>
@@ -1181,18 +1175,18 @@
         <v>2</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
-        <v>46137</v>
+        <v>46270</v>
       </c>
       <c r="B12" t="s">
-        <v>99</v>
+        <v>26</v>
       </c>
       <c r="C12" t="s">
-        <v>116</v>
+        <v>23</v>
       </c>
       <c r="D12">
         <f>VLOOKUP(B12,Teams!A:B,2,FALSE)</f>
@@ -1203,18 +1197,18 @@
         <v>2</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
-        <v>46137</v>
+        <v>46270</v>
       </c>
       <c r="B13" t="s">
-        <v>105</v>
+        <v>85</v>
       </c>
       <c r="C13" t="s">
-        <v>48</v>
+        <v>16</v>
       </c>
       <c r="D13">
         <f>VLOOKUP(B13,Teams!A:B,2,FALSE)</f>
@@ -1225,18 +1219,18 @@
         <v>2</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
-        <v>46137</v>
+        <v>46270</v>
       </c>
       <c r="B14" t="s">
-        <v>115</v>
+        <v>103</v>
       </c>
       <c r="C14" t="s">
-        <v>104</v>
+        <v>33</v>
       </c>
       <c r="D14">
         <f>VLOOKUP(B14,Teams!A:B,2,FALSE)</f>
@@ -1247,18 +1241,18 @@
         <v>2</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
-        <v>46137</v>
+        <v>46270</v>
       </c>
       <c r="B15" t="s">
-        <v>125</v>
+        <v>105</v>
       </c>
       <c r="C15" t="s">
-        <v>103</v>
+        <v>83</v>
       </c>
       <c r="D15">
         <f>VLOOKUP(B15,Teams!A:B,2,FALSE)</f>
@@ -1269,106 +1263,106 @@
         <v>2</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
-        <v>46137</v>
+        <v>46270</v>
       </c>
       <c r="B16" t="s">
-        <v>49</v>
+        <v>115</v>
       </c>
       <c r="C16" t="s">
-        <v>123</v>
+        <v>95</v>
       </c>
       <c r="D16">
         <f>VLOOKUP(B16,Teams!A:B,2,FALSE)</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E16">
         <f>VLOOKUP(C16,Teams!A:B,2,FALSE)</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
-        <v>46137</v>
+        <v>46270</v>
       </c>
       <c r="B17" t="s">
-        <v>124</v>
+        <v>136</v>
       </c>
       <c r="C17" t="s">
-        <v>100</v>
+        <v>135</v>
       </c>
       <c r="D17">
         <f>VLOOKUP(B17,Teams!A:B,2,FALSE)</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E17">
         <f>VLOOKUP(C17,Teams!A:B,2,FALSE)</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
-        <v>46137</v>
+        <v>46270</v>
       </c>
       <c r="B18" t="s">
-        <v>15</v>
+        <v>137</v>
       </c>
       <c r="C18" t="s">
-        <v>72</v>
+        <v>48</v>
       </c>
       <c r="D18">
         <f>VLOOKUP(B18,Teams!A:B,2,FALSE)</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E18">
         <f>VLOOKUP(C18,Teams!A:B,2,FALSE)</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
-        <v>46137</v>
+        <v>46270</v>
       </c>
       <c r="B19" t="s">
-        <v>19</v>
+        <v>128</v>
       </c>
       <c r="C19" t="s">
-        <v>16</v>
+        <v>143</v>
       </c>
       <c r="D19">
         <f>VLOOKUP(B19,Teams!A:B,2,FALSE)</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E19">
         <f>VLOOKUP(C19,Teams!A:B,2,FALSE)</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
-        <v>46137</v>
+        <v>46270</v>
       </c>
       <c r="B20" t="s">
-        <v>27</v>
+        <v>100</v>
       </c>
       <c r="C20" t="s">
-        <v>52</v>
+        <v>116</v>
       </c>
       <c r="D20">
         <f>VLOOKUP(B20,Teams!A:B,2,FALSE)</f>
@@ -1379,18 +1373,18 @@
         <v>3</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
-        <v>46137</v>
+        <v>46270</v>
       </c>
       <c r="B21" t="s">
-        <v>33</v>
+        <v>138</v>
       </c>
       <c r="C21" t="s">
-        <v>93</v>
+        <v>124</v>
       </c>
       <c r="D21">
         <f>VLOOKUP(B21,Teams!A:B,2,FALSE)</f>
@@ -1401,18 +1395,18 @@
         <v>3</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
-        <v>46137</v>
+        <v>46270</v>
       </c>
       <c r="B22" t="s">
-        <v>65</v>
+        <v>11</v>
       </c>
       <c r="C22" t="s">
-        <v>81</v>
+        <v>123</v>
       </c>
       <c r="D22">
         <f>VLOOKUP(B22,Teams!A:B,2,FALSE)</f>
@@ -1423,18 +1417,18 @@
         <v>3</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
-        <v>46137</v>
+        <v>46270</v>
       </c>
       <c r="B23" t="s">
-        <v>73</v>
+        <v>19</v>
       </c>
       <c r="C23" t="s">
-        <v>144</v>
+        <v>81</v>
       </c>
       <c r="D23">
         <f>VLOOKUP(B23,Teams!A:B,2,FALSE)</f>
@@ -1445,18 +1439,18 @@
         <v>3</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
-        <v>46137</v>
+        <v>46270</v>
       </c>
       <c r="B24" t="s">
-        <v>76</v>
+        <v>27</v>
       </c>
       <c r="C24" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="D24">
         <f>VLOOKUP(B24,Teams!A:B,2,FALSE)</f>
@@ -1467,18 +1461,18 @@
         <v>3</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
-        <v>46137</v>
+        <v>46270</v>
       </c>
       <c r="B25" t="s">
+        <v>49</v>
+      </c>
+      <c r="C25" t="s">
         <v>101</v>
-      </c>
-      <c r="C25" t="s">
-        <v>102</v>
       </c>
       <c r="D25">
         <f>VLOOKUP(B25,Teams!A:B,2,FALSE)</f>
@@ -1489,18 +1483,18 @@
         <v>3</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
-        <v>46137</v>
+        <v>46270</v>
       </c>
       <c r="B26" t="s">
-        <v>110</v>
+        <v>65</v>
       </c>
       <c r="C26" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="D26">
         <f>VLOOKUP(B26,Teams!A:B,2,FALSE)</f>
@@ -1514,15 +1508,15 @@
         <v>154</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
-        <v>46137</v>
+        <v>46270</v>
       </c>
       <c r="B27" t="s">
-        <v>138</v>
+        <v>71</v>
       </c>
       <c r="C27" t="s">
-        <v>1</v>
+        <v>99</v>
       </c>
       <c r="D27">
         <f>VLOOKUP(B27,Teams!A:B,2,FALSE)</f>
@@ -1533,84 +1527,84 @@
         <v>3</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="2">
-        <v>46137</v>
+        <v>46270</v>
       </c>
       <c r="B28" t="s">
-        <v>60</v>
+        <v>76</v>
       </c>
       <c r="C28" t="s">
-        <v>129</v>
+        <v>72</v>
       </c>
       <c r="D28">
         <f>VLOOKUP(B28,Teams!A:B,2,FALSE)</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E28">
         <f>VLOOKUP(C28,Teams!A:B,2,FALSE)</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="2">
-        <v>46137</v>
+        <v>46270</v>
       </c>
       <c r="B29" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="C29" t="s">
-        <v>133</v>
+        <v>15</v>
       </c>
       <c r="D29">
         <f>VLOOKUP(B29,Teams!A:B,2,FALSE)</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E29">
         <f>VLOOKUP(C29,Teams!A:B,2,FALSE)</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="2">
-        <v>46137</v>
+        <v>46270</v>
       </c>
       <c r="B30" t="s">
-        <v>4</v>
+        <v>144</v>
       </c>
       <c r="C30" t="s">
-        <v>42</v>
+        <v>86</v>
       </c>
       <c r="D30">
         <f>VLOOKUP(B30,Teams!A:B,2,FALSE)</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E30">
         <f>VLOOKUP(C30,Teams!A:B,2,FALSE)</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="2">
-        <v>46137</v>
+        <v>46270</v>
       </c>
       <c r="B31" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="C31" t="s">
-        <v>58</v>
+        <v>117</v>
       </c>
       <c r="D31">
         <f>VLOOKUP(B31,Teams!A:B,2,FALSE)</f>
@@ -1621,18 +1615,18 @@
         <v>4</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="2">
-        <v>46137</v>
+        <v>46270</v>
       </c>
       <c r="B32" t="s">
-        <v>24</v>
+        <v>112</v>
       </c>
       <c r="C32" t="s">
-        <v>37</v>
+        <v>102</v>
       </c>
       <c r="D32">
         <f>VLOOKUP(B32,Teams!A:B,2,FALSE)</f>
@@ -1643,18 +1637,18 @@
         <v>4</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="2">
-        <v>46137</v>
+        <v>46270</v>
       </c>
       <c r="B33" t="s">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="C33" t="s">
-        <v>12</v>
+        <v>42</v>
       </c>
       <c r="D33">
         <f>VLOOKUP(B33,Teams!A:B,2,FALSE)</f>
@@ -1668,15 +1662,15 @@
         <v>167</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="2">
-        <v>46137</v>
+        <v>46270</v>
       </c>
       <c r="B34" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="C34" t="s">
-        <v>43</v>
+        <v>110</v>
       </c>
       <c r="D34">
         <f>VLOOKUP(B34,Teams!A:B,2,FALSE)</f>
@@ -1687,18 +1681,18 @@
         <v>4</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="2">
-        <v>46137</v>
+        <v>46270</v>
       </c>
       <c r="B35" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C35" t="s">
-        <v>97</v>
+        <v>60</v>
       </c>
       <c r="D35">
         <f>VLOOKUP(B35,Teams!A:B,2,FALSE)</f>
@@ -1709,18 +1703,18 @@
         <v>4</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="2">
-        <v>46137</v>
+        <v>46270</v>
       </c>
       <c r="B36" t="s">
-        <v>92</v>
+        <v>39</v>
       </c>
       <c r="C36" t="s">
-        <v>98</v>
+        <v>10</v>
       </c>
       <c r="D36">
         <f>VLOOKUP(B36,Teams!A:B,2,FALSE)</f>
@@ -1731,18 +1725,18 @@
         <v>4</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="2">
-        <v>46137</v>
+        <v>46270</v>
       </c>
       <c r="B37" t="s">
-        <v>117</v>
+        <v>43</v>
       </c>
       <c r="C37" t="s">
-        <v>53</v>
+        <v>146</v>
       </c>
       <c r="D37">
         <f>VLOOKUP(B37,Teams!A:B,2,FALSE)</f>
@@ -1753,18 +1747,18 @@
         <v>4</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="2">
-        <v>46137</v>
+        <v>46270</v>
       </c>
       <c r="B38" t="s">
+        <v>52</v>
+      </c>
+      <c r="C38" t="s">
         <v>134</v>
-      </c>
-      <c r="C38" t="s">
-        <v>62</v>
       </c>
       <c r="D38">
         <f>VLOOKUP(B38,Teams!A:B,2,FALSE)</f>
@@ -1775,26 +1769,162 @@
         <v>4</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A39" s="2"/>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A40" s="2"/>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A41" s="2"/>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A42" s="2"/>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A43" s="2"/>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A44" s="2"/>
+        <v>159</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39" s="2">
+        <v>46270</v>
+      </c>
+      <c r="B39" t="s">
+        <v>93</v>
+      </c>
+      <c r="C39" t="s">
+        <v>92</v>
+      </c>
+      <c r="D39">
+        <f>VLOOKUP(B39,Teams!A:B,2,FALSE)</f>
+        <v>4</v>
+      </c>
+      <c r="E39">
+        <f>VLOOKUP(C39,Teams!A:B,2,FALSE)</f>
+        <v>4</v>
+      </c>
+      <c r="F39" s="3" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" s="2">
+        <v>46270</v>
+      </c>
+      <c r="B40" t="s">
+        <v>107</v>
+      </c>
+      <c r="C40" t="s">
+        <v>58</v>
+      </c>
+      <c r="D40">
+        <f>VLOOKUP(B40,Teams!A:B,2,FALSE)</f>
+        <v>4</v>
+      </c>
+      <c r="E40">
+        <f>VLOOKUP(C40,Teams!A:B,2,FALSE)</f>
+        <v>4</v>
+      </c>
+      <c r="F40" s="3" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" s="2">
+        <v>46270</v>
+      </c>
+      <c r="B41" t="s">
+        <v>129</v>
+      </c>
+      <c r="C41" t="s">
+        <v>40</v>
+      </c>
+      <c r="D41">
+        <f>VLOOKUP(B41,Teams!A:B,2,FALSE)</f>
+        <v>4</v>
+      </c>
+      <c r="E41">
+        <f>VLOOKUP(C41,Teams!A:B,2,FALSE)</f>
+        <v>4</v>
+      </c>
+      <c r="F41" s="3" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42" s="2">
+        <v>46270</v>
+      </c>
+      <c r="B42" t="s">
+        <v>133</v>
+      </c>
+      <c r="C42" t="s">
+        <v>98</v>
+      </c>
+      <c r="D42">
+        <f>VLOOKUP(B42,Teams!A:B,2,FALSE)</f>
+        <v>4</v>
+      </c>
+      <c r="E42">
+        <f>VLOOKUP(C42,Teams!A:B,2,FALSE)</f>
+        <v>4</v>
+      </c>
+      <c r="F42" s="3" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43" s="2">
+        <v>46271</v>
+      </c>
+      <c r="B43" t="s">
+        <v>51</v>
+      </c>
+      <c r="C43" t="s">
+        <v>80</v>
+      </c>
+      <c r="D43">
+        <f>VLOOKUP(B43,Teams!A:B,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="E43">
+        <f>VLOOKUP(C43,Teams!A:B,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A44" s="2">
+        <v>46271</v>
+      </c>
+      <c r="B44" t="s">
+        <v>7</v>
+      </c>
+      <c r="C44" t="s">
+        <v>36</v>
+      </c>
+      <c r="D44">
+        <f>VLOOKUP(B44,Teams!A:B,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="E44">
+        <f>VLOOKUP(C44,Teams!A:B,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A45" s="2">
+        <v>46271</v>
+      </c>
+      <c r="B45" t="s">
+        <v>13</v>
+      </c>
+      <c r="C45" t="s">
+        <v>141</v>
+      </c>
+      <c r="D45">
+        <f>VLOOKUP(B45,Teams!A:B,2,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="E45">
+        <f>VLOOKUP(C45,Teams!A:B,2,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>168</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1816,13 +1946,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{660D5CBD-EF61-4F28-8F5F-C3B953B1D14A}">
   <dimension ref="A1:B147"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="23" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.7265625" style="1"/>
+    <col min="2" max="2" width="8.7109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1830,7 +1960,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -1838,7 +1968,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -1846,7 +1976,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1854,7 +1984,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -1862,7 +1992,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -1870,7 +2000,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -1878,7 +2008,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -1886,7 +2016,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>8</v>
       </c>
@@ -1894,7 +2024,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>9</v>
       </c>
@@ -1902,7 +2032,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>10</v>
       </c>
@@ -1910,7 +2040,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>11</v>
       </c>
@@ -1918,15 +2048,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>12</v>
       </c>
-      <c r="B13" s="1">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B13" s="1" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>13</v>
       </c>
@@ -1934,7 +2064,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>14</v>
       </c>
@@ -1942,7 +2072,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>15</v>
       </c>
@@ -1950,15 +2080,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>16</v>
       </c>
       <c r="B17" s="1">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>17</v>
       </c>
@@ -1966,7 +2096,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>18</v>
       </c>
@@ -1974,7 +2104,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>19</v>
       </c>
@@ -1982,7 +2112,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>20</v>
       </c>
@@ -1990,7 +2120,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>21</v>
       </c>
@@ -1998,7 +2128,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>22</v>
       </c>
@@ -2006,7 +2136,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>23</v>
       </c>
@@ -2014,7 +2144,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>24</v>
       </c>
@@ -2022,23 +2152,23 @@
         <v>4</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>25</v>
       </c>
       <c r="B26" s="1">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>26</v>
       </c>
       <c r="B27" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>27</v>
       </c>
@@ -2046,7 +2176,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>28</v>
       </c>
@@ -2054,7 +2184,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>29</v>
       </c>
@@ -2062,7 +2192,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>30</v>
       </c>
@@ -2070,7 +2200,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>31</v>
       </c>
@@ -2078,23 +2208,23 @@
         <v>148</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>32</v>
       </c>
       <c r="B33" s="1">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>33</v>
       </c>
       <c r="B34" s="1">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>34</v>
       </c>
@@ -2102,7 +2232,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>35</v>
       </c>
@@ -2110,7 +2240,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>36</v>
       </c>
@@ -2118,7 +2248,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>37</v>
       </c>
@@ -2126,7 +2256,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>38</v>
       </c>
@@ -2134,7 +2264,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>39</v>
       </c>
@@ -2142,7 +2272,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>40</v>
       </c>
@@ -2150,15 +2280,15 @@
         <v>4</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>41</v>
       </c>
       <c r="B42" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>42</v>
       </c>
@@ -2166,7 +2296,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>43</v>
       </c>
@@ -2174,7 +2304,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>44</v>
       </c>
@@ -2182,7 +2312,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>45</v>
       </c>
@@ -2190,7 +2320,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>46</v>
       </c>
@@ -2198,7 +2328,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>47</v>
       </c>
@@ -2206,7 +2336,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>48</v>
       </c>
@@ -2214,7 +2344,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>49</v>
       </c>
@@ -2222,7 +2352,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>50</v>
       </c>
@@ -2230,7 +2360,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>51</v>
       </c>
@@ -2238,15 +2368,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>52</v>
       </c>
       <c r="B53" s="1">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.35">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>53</v>
       </c>
@@ -2254,7 +2384,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>54</v>
       </c>
@@ -2262,7 +2392,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>55</v>
       </c>
@@ -2270,7 +2400,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>56</v>
       </c>
@@ -2278,7 +2408,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>57</v>
       </c>
@@ -2286,7 +2416,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>58</v>
       </c>
@@ -2294,7 +2424,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>59</v>
       </c>
@@ -2302,7 +2432,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>60</v>
       </c>
@@ -2310,7 +2440,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>61</v>
       </c>
@@ -2318,15 +2448,15 @@
         <v>148</v>
       </c>
     </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>62</v>
       </c>
-      <c r="B63" s="1">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B63" s="1" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>63</v>
       </c>
@@ -2334,7 +2464,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>64</v>
       </c>
@@ -2342,7 +2472,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>65</v>
       </c>
@@ -2350,23 +2480,23 @@
         <v>3</v>
       </c>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>66</v>
       </c>
       <c r="B67" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>67</v>
       </c>
       <c r="B68" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>68</v>
       </c>
@@ -2374,7 +2504,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>69</v>
       </c>
@@ -2382,7 +2512,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>70</v>
       </c>
@@ -2390,15 +2520,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>71</v>
       </c>
       <c r="B72" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.35">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>72</v>
       </c>
@@ -2406,15 +2536,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>73</v>
       </c>
       <c r="B74" s="1">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.35">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>74</v>
       </c>
@@ -2422,7 +2552,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>75</v>
       </c>
@@ -2430,7 +2560,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>76</v>
       </c>
@@ -2438,7 +2568,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>77</v>
       </c>
@@ -2446,7 +2576,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>78</v>
       </c>
@@ -2454,7 +2584,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>79</v>
       </c>
@@ -2462,7 +2592,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>80</v>
       </c>
@@ -2470,7 +2600,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>81</v>
       </c>
@@ -2478,7 +2608,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>82</v>
       </c>
@@ -2486,7 +2616,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>83</v>
       </c>
@@ -2494,7 +2624,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>84</v>
       </c>
@@ -2502,7 +2632,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>85</v>
       </c>
@@ -2510,15 +2640,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>86</v>
       </c>
       <c r="B87" s="1">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.35">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>87</v>
       </c>
@@ -2526,7 +2656,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>88</v>
       </c>
@@ -2534,7 +2664,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>89</v>
       </c>
@@ -2542,7 +2672,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>90</v>
       </c>
@@ -2550,7 +2680,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>91</v>
       </c>
@@ -2558,7 +2688,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>92</v>
       </c>
@@ -2566,15 +2696,15 @@
         <v>4</v>
       </c>
     </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>93</v>
       </c>
       <c r="B94" s="1">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.35">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>94</v>
       </c>
@@ -2582,7 +2712,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>95</v>
       </c>
@@ -2590,7 +2720,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>96</v>
       </c>
@@ -2598,15 +2728,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>97</v>
       </c>
       <c r="B98" s="1">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.35">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>98</v>
       </c>
@@ -2614,15 +2744,15 @@
         <v>4</v>
       </c>
     </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>99</v>
       </c>
       <c r="B100" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.35">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>100</v>
       </c>
@@ -2630,7 +2760,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="102" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>101</v>
       </c>
@@ -2638,15 +2768,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="103" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>102</v>
       </c>
       <c r="B103" s="1">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="104" spans="1:2" x14ac:dyDescent="0.35">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>103</v>
       </c>
@@ -2654,7 +2784,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="105" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>104</v>
       </c>
@@ -2662,7 +2792,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="106" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>105</v>
       </c>
@@ -2670,7 +2800,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="107" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>106</v>
       </c>
@@ -2678,15 +2808,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="108" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>107</v>
       </c>
-      <c r="B108" s="1" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="109" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B108" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>108</v>
       </c>
@@ -2694,7 +2824,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="110" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>109</v>
       </c>
@@ -2702,15 +2832,15 @@
         <v>148</v>
       </c>
     </row>
-    <row r="111" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>110</v>
       </c>
       <c r="B111" s="1">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="112" spans="1:2" x14ac:dyDescent="0.35">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>111</v>
       </c>
@@ -2718,7 +2848,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="113" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>112</v>
       </c>
@@ -2726,7 +2856,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="114" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>113</v>
       </c>
@@ -2734,7 +2864,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="115" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>114</v>
       </c>
@@ -2742,7 +2872,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="116" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>115</v>
       </c>
@@ -2750,15 +2880,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="117" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>116</v>
       </c>
       <c r="B117" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="118" spans="1:2" x14ac:dyDescent="0.35">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>117</v>
       </c>
@@ -2766,7 +2896,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="119" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>118</v>
       </c>
@@ -2774,7 +2904,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="120" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>119</v>
       </c>
@@ -2782,7 +2912,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="121" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>120</v>
       </c>
@@ -2790,7 +2920,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="122" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>121</v>
       </c>
@@ -2798,7 +2928,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="123" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>122</v>
       </c>
@@ -2806,7 +2936,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="124" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>123</v>
       </c>
@@ -2814,7 +2944,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="125" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>124</v>
       </c>
@@ -2822,7 +2952,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="126" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>125</v>
       </c>
@@ -2830,7 +2960,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="127" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>126</v>
       </c>
@@ -2838,7 +2968,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="128" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>127</v>
       </c>
@@ -2846,7 +2976,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="129" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>128</v>
       </c>
@@ -2854,7 +2984,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="130" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>129</v>
       </c>
@@ -2862,7 +2992,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="131" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>130</v>
       </c>
@@ -2870,7 +3000,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="132" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>131</v>
       </c>
@@ -2878,7 +3008,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="133" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>132</v>
       </c>
@@ -2886,7 +3016,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="134" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>133</v>
       </c>
@@ -2894,7 +3024,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="135" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>134</v>
       </c>
@@ -2902,7 +3032,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="136" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>135</v>
       </c>
@@ -2910,7 +3040,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="137" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>136</v>
       </c>
@@ -2918,15 +3048,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="138" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>137</v>
       </c>
       <c r="B138" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="139" spans="1:2" x14ac:dyDescent="0.35">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="139" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>138</v>
       </c>
@@ -2934,7 +3064,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="140" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>139</v>
       </c>
@@ -2942,7 +3072,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="141" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>140</v>
       </c>
@@ -2950,15 +3080,15 @@
         <v>148</v>
       </c>
     </row>
-    <row r="142" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>141</v>
       </c>
       <c r="B142" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="143" spans="1:2" x14ac:dyDescent="0.35">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="143" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>142</v>
       </c>
@@ -2966,7 +3096,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="144" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>143</v>
       </c>
@@ -2974,7 +3104,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="145" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>144</v>
       </c>
@@ -2982,7 +3112,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="146" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>145</v>
       </c>
@@ -2990,12 +3120,12 @@
         <v>148</v>
       </c>
     </row>
-    <row r="147" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>146</v>
       </c>
-      <c r="B147" s="1" t="s">
-        <v>148</v>
+      <c r="B147" s="1">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
